--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.carotenes/Resultats_total.carotenes_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.carotenes/Resultats_total.carotenes_moy_RMSEP.xlsx
@@ -1,21 +1,220 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\total.carotenes\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+  <si>
+    <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>RMSEP_glo</t>
+  </si>
+  <si>
+    <t>LV1_RMSEP</t>
+  </si>
+  <si>
+    <t>LV2_RMSEP</t>
+  </si>
+  <si>
+    <t>LV3_RMSEP</t>
+  </si>
+  <si>
+    <t>LV4_RMSEP</t>
+  </si>
+  <si>
+    <t>LV5_RMSEP</t>
+  </si>
+  <si>
+    <t>LV6_RMSEP</t>
+  </si>
+  <si>
+    <t>LV7_RMSEP</t>
+  </si>
+  <si>
+    <t>LV8_RMSEP</t>
+  </si>
+  <si>
+    <t>LV9_RMSEP</t>
+  </si>
+  <si>
+    <t>LV10_RMSEP</t>
+  </si>
+  <si>
+    <t>LV11_RMSEP</t>
+  </si>
+  <si>
+    <t>LV12_RMSEP</t>
+  </si>
+  <si>
+    <t>LV13_RMSEP</t>
+  </si>
+  <si>
+    <t>LV14_RMSEP</t>
+  </si>
+  <si>
+    <t>LV15_RMSEP</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1000,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(1,3,5)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -61,13 +260,40 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +335,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +367,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +402,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,190 +578,156 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pretraitement</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>RMSEP_glo</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LV1_RMSEP</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LV2_RMSEP</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LV3_RMSEP</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LV4_RMSEP</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LV5_RMSEP</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LV6_RMSEP</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LV7_RMSEP</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LV8_RMSEP</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LV9_RMSEP</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LV10_RMSEP</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LV11_RMSEP</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LV12_RMSEP</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LV13_RMSEP</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>LV14_RMSEP</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>LV15_RMSEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1000,1)_snv_</t>
-        </is>
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
       </c>
       <c r="B2">
         <v>495.1161531195043</v>
       </c>
       <c r="C2">
-        <v>603.6519221773655</v>
+        <v>603.65192217736546</v>
       </c>
       <c r="D2">
-        <v>517.1355343070503</v>
+        <v>517.13553430705031</v>
       </c>
       <c r="E2">
-        <v>496.076082022556</v>
+        <v>496.07608202255602</v>
       </c>
       <c r="F2">
-        <v>472.1999094233462</v>
+        <v>472.19990942334618</v>
       </c>
       <c r="G2">
-        <v>464.0794604974867</v>
+        <v>464.07946049748671</v>
       </c>
       <c r="H2">
         <v>450.9424700505171</v>
       </c>
       <c r="I2">
-        <v>446.3682443553213</v>
+        <v>446.36824435532128</v>
       </c>
       <c r="J2">
-        <v>452.8506448599409</v>
+        <v>452.85064485994093</v>
       </c>
       <c r="K2">
-        <v>461.6497278993627</v>
+        <v>461.64972789936269</v>
       </c>
       <c r="L2">
-        <v>472.8118588829904</v>
+        <v>472.81185888299041</v>
       </c>
       <c r="M2">
-        <v>475.2839544265456</v>
+        <v>475.28395442654562</v>
       </c>
       <c r="N2">
         <v>496.7770560613701</v>
       </c>
       <c r="O2">
-        <v>516.3198683372423</v>
+        <v>516.31986833724227</v>
       </c>
       <c r="P2">
-        <v>523.9750392550417</v>
+        <v>523.97503925504168</v>
       </c>
       <c r="Q2">
-        <v>511.8512101852368</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>511.85121018523682</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>523.1971489725806</v>
+        <v>523.19714897258064</v>
       </c>
       <c r="C3">
-        <v>564.8902860739353</v>
+        <v>564.89028607393527</v>
       </c>
       <c r="D3">
-        <v>508.3556104225166</v>
+        <v>508.35561042251658</v>
       </c>
       <c r="E3">
-        <v>506.8286159649244</v>
+        <v>506.82861596492438</v>
       </c>
       <c r="F3">
-        <v>503.0961985291817</v>
+        <v>503.09619852918172</v>
       </c>
       <c r="G3">
-        <v>510.7534365084888</v>
+        <v>510.75343650848879</v>
       </c>
       <c r="H3">
-        <v>513.1310562814921</v>
+        <v>513.13105628149208</v>
       </c>
       <c r="I3">
         <v>536.9876094776015</v>
       </c>
       <c r="J3">
-        <v>543.0331363914336</v>
+        <v>543.03313639143357</v>
       </c>
       <c r="K3">
-        <v>551.0486939275336</v>
+        <v>551.04869392753358</v>
       </c>
       <c r="L3">
-        <v>547.7194599894044</v>
+        <v>547.71945998940441</v>
       </c>
       <c r="M3">
         <v>558.3171705354539</v>
@@ -542,460 +736,442 @@
         <v>587.1935736747198</v>
       </c>
       <c r="O3">
-        <v>616.9477081194419</v>
+        <v>616.94770811944193</v>
       </c>
       <c r="P3">
-        <v>637.0699638065017</v>
+        <v>637.06996380650173</v>
       </c>
       <c r="Q3">
-        <v>656.4229029680157</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>656.42290296801571</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
       </c>
       <c r="B4">
-        <v>535.8995106132458</v>
+        <v>535.89951061324575</v>
       </c>
       <c r="C4">
-        <v>593.3415002964678</v>
+        <v>593.34150029646776</v>
       </c>
       <c r="D4">
-        <v>525.4633393586251</v>
+        <v>525.46333935862515</v>
       </c>
       <c r="E4">
-        <v>517.4029825982097</v>
+        <v>517.40298259820975</v>
       </c>
       <c r="F4">
-        <v>516.8757855010376</v>
+        <v>516.87578550103763</v>
       </c>
       <c r="G4">
-        <v>508.6611318427027</v>
+        <v>508.66113184270267</v>
       </c>
       <c r="H4">
-        <v>491.0572053253167</v>
+        <v>491.05720532531672</v>
       </c>
       <c r="I4">
-        <v>475.7550039156745</v>
+        <v>475.75500391567448</v>
       </c>
       <c r="J4">
-        <v>490.9761311915059</v>
+        <v>490.97613119150589</v>
       </c>
       <c r="K4">
-        <v>500.3431353286825</v>
+        <v>500.34313532868248</v>
       </c>
       <c r="L4">
-        <v>533.4274932594158</v>
+        <v>533.42749325941577</v>
       </c>
       <c r="M4">
-        <v>543.8771670279153</v>
+        <v>543.87716702791533</v>
       </c>
       <c r="N4">
-        <v>534.5850801183307</v>
+        <v>534.58508011833067</v>
       </c>
       <c r="O4">
         <v>532.4435001145082</v>
       </c>
       <c r="P4">
-        <v>536.5090585047377</v>
+        <v>536.50905850473771</v>
       </c>
       <c r="Q4">
-        <v>534.742377556079</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-        </is>
+        <v>534.74237755607896</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>517.4000661809685</v>
+        <v>517.40006618096845</v>
       </c>
       <c r="C5">
-        <v>512.9471255776324</v>
+        <v>512.94712557763239</v>
       </c>
       <c r="D5">
-        <v>511.4747341276801</v>
+        <v>511.47473412768011</v>
       </c>
       <c r="E5">
-        <v>510.1860307297563</v>
+        <v>510.18603072975628</v>
       </c>
       <c r="F5">
-        <v>515.3686719288992</v>
+        <v>515.36867192889918</v>
       </c>
       <c r="G5">
-        <v>517.6310871568352</v>
+        <v>517.63108715683518</v>
       </c>
       <c r="H5">
-        <v>515.6974501148671</v>
+        <v>515.69745011486714</v>
       </c>
       <c r="I5">
-        <v>518.004170704051</v>
+        <v>518.00417070405103</v>
       </c>
       <c r="J5">
-        <v>523.4942597790355</v>
+        <v>523.49425977903547</v>
       </c>
       <c r="K5">
-        <v>535.4276471293222</v>
+        <v>535.42764712932217</v>
       </c>
       <c r="L5">
-        <v>539.2181120725127</v>
+        <v>539.21811207251267</v>
       </c>
       <c r="M5">
-        <v>543.7548594742883</v>
+        <v>543.75485947428831</v>
       </c>
       <c r="N5">
-        <v>550.2454693819543</v>
+        <v>550.24546938195431</v>
       </c>
       <c r="O5">
-        <v>551.6552689220584</v>
+        <v>551.65526892205844</v>
       </c>
       <c r="P5">
-        <v>559.2650385373246</v>
+        <v>559.26503853732459</v>
       </c>
       <c r="Q5">
-        <v>552.6236800520805</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-        </is>
+        <v>552.62368005208054</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>517.2580283635367</v>
+        <v>517.25802836353671</v>
       </c>
       <c r="C6">
-        <v>512.1996368957874</v>
+        <v>512.19963689578742</v>
       </c>
       <c r="D6">
-        <v>508.6830026944206</v>
+        <v>508.68300269442062</v>
       </c>
       <c r="E6">
-        <v>506.4273166937522</v>
+        <v>506.42731669375218</v>
       </c>
       <c r="F6">
-        <v>515.5485137174693</v>
+        <v>515.54851371746929</v>
       </c>
       <c r="G6">
-        <v>503.6958467204925</v>
+        <v>503.69584672049251</v>
       </c>
       <c r="H6">
-        <v>521.4640130104237</v>
+        <v>521.46401301042374</v>
       </c>
       <c r="I6">
-        <v>518.0443299517545</v>
+        <v>518.04432995175455</v>
       </c>
       <c r="J6">
-        <v>530.6379443418992</v>
+        <v>530.63794434189924</v>
       </c>
       <c r="K6">
-        <v>533.0050363615684</v>
+        <v>533.00503636156839</v>
       </c>
       <c r="L6">
-        <v>539.548986363992</v>
+        <v>539.54898636399196</v>
       </c>
       <c r="M6">
-        <v>556.4145665563279</v>
+        <v>556.41456655632794</v>
       </c>
       <c r="N6">
         <v>573.5331247139967</v>
       </c>
       <c r="O6">
-        <v>586.0430591351235</v>
+        <v>586.04305913512349</v>
       </c>
       <c r="P6">
-        <v>586.6323713758642</v>
+        <v>586.63237137586418</v>
       </c>
       <c r="Q6">
-        <v>570.3350055260112</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>570.33500552601117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>462.9251306063443</v>
+        <v>462.92513060634428</v>
       </c>
       <c r="C7">
-        <v>594.4940226509987</v>
+        <v>594.49402265099866</v>
       </c>
       <c r="D7">
         <v>517.7359404524791</v>
       </c>
       <c r="E7">
-        <v>472.8788430248605</v>
+        <v>472.87884302486049</v>
       </c>
       <c r="F7">
-        <v>447.2243093279739</v>
+        <v>447.22430932797391</v>
       </c>
       <c r="G7">
-        <v>434.0669157494079</v>
+        <v>434.06691574940788</v>
       </c>
       <c r="H7">
-        <v>425.7411223461793</v>
+        <v>425.74112234617928</v>
       </c>
       <c r="I7">
-        <v>436.567173410596</v>
+        <v>436.56717341059601</v>
       </c>
       <c r="J7">
-        <v>443.7198632207896</v>
+        <v>443.71986322078959</v>
       </c>
       <c r="K7">
-        <v>453.1753226019327</v>
+        <v>453.17532260193269</v>
       </c>
       <c r="L7">
-        <v>452.321265575475</v>
+        <v>452.32126557547502</v>
       </c>
       <c r="M7">
         <v>486.9977907423476</v>
       </c>
       <c r="N7">
-        <v>486.2701393208499</v>
+        <v>486.27013932084992</v>
       </c>
       <c r="O7">
-        <v>477.68972198378</v>
+        <v>477.68972198377998</v>
       </c>
       <c r="P7">
-        <v>478.6712065126259</v>
+        <v>478.67120651262587</v>
       </c>
       <c r="Q7">
-        <v>478.8909981331599</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>478.89099813315988</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>526.6006309843424</v>
+        <v>526.60063098434239</v>
       </c>
       <c r="C8">
-        <v>565.2034618483677</v>
+        <v>565.20346184836774</v>
       </c>
       <c r="D8">
-        <v>528.3634676203203</v>
+        <v>528.36346762032031</v>
       </c>
       <c r="E8">
-        <v>499.2386841186587</v>
+        <v>499.23868411865868</v>
       </c>
       <c r="F8">
-        <v>487.1228052052678</v>
+        <v>487.12280520526781</v>
       </c>
       <c r="G8">
-        <v>485.0103561663627</v>
+        <v>485.01035616636273</v>
       </c>
       <c r="H8">
-        <v>487.8136143819524</v>
+        <v>487.81361438195239</v>
       </c>
       <c r="I8">
         <v>480.1520510162365</v>
       </c>
       <c r="J8">
-        <v>475.5804814836791</v>
+        <v>475.58048148367908</v>
       </c>
       <c r="K8">
         <v>509.5834611422278</v>
       </c>
       <c r="L8">
-        <v>529.1145221464769</v>
+        <v>529.11452214647693</v>
       </c>
       <c r="M8">
-        <v>531.074384212225</v>
+        <v>531.07438421222503</v>
       </c>
       <c r="N8">
-        <v>524.6046687801663</v>
+        <v>524.60466878016632</v>
       </c>
       <c r="O8">
-        <v>510.7404904431772</v>
+        <v>510.74049044317718</v>
       </c>
       <c r="P8">
-        <v>521.6665130038585</v>
+        <v>521.66651300385854</v>
       </c>
       <c r="Q8">
-        <v>519.3632678750862</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-        </is>
+        <v>519.36326787508619</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>530.0920795664335</v>
+        <v>530.09207956643354</v>
       </c>
       <c r="C9">
-        <v>564.3179732328342</v>
+        <v>564.31797323283422</v>
       </c>
       <c r="D9">
-        <v>527.673589900122</v>
+        <v>527.67358990012201</v>
       </c>
       <c r="E9">
-        <v>501.6079982289803</v>
+        <v>501.60799822898031</v>
       </c>
       <c r="F9">
-        <v>491.4197399460215</v>
+        <v>491.41973994602148</v>
       </c>
       <c r="G9">
-        <v>487.3516239194053</v>
+        <v>487.35162391940531</v>
       </c>
       <c r="H9">
-        <v>489.3754378035601</v>
+        <v>489.37543780356009</v>
       </c>
       <c r="I9">
         <v>484.3937459231629</v>
       </c>
       <c r="J9">
-        <v>478.6460371894476</v>
+        <v>478.64603718944761</v>
       </c>
       <c r="K9">
-        <v>500.0282697788455</v>
+        <v>500.02826977884553</v>
       </c>
       <c r="L9">
-        <v>519.8255858224074</v>
+        <v>519.82558582240745</v>
       </c>
       <c r="M9">
-        <v>530.0889754863251</v>
+        <v>530.08897548632513</v>
       </c>
       <c r="N9">
         <v>522.1018022086962</v>
       </c>
       <c r="O9">
-        <v>505.998143319775</v>
+        <v>505.99814331977501</v>
       </c>
       <c r="P9">
-        <v>515.9465881965294</v>
+        <v>515.94658819652943</v>
       </c>
       <c r="Q9">
-        <v>517.104821207032</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-        </is>
+        <v>517.10482120703205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>539.6502012446234</v>
+        <v>539.65020124462342</v>
       </c>
       <c r="C10">
-        <v>565.0695414463736</v>
+        <v>565.06954144637359</v>
       </c>
       <c r="D10">
-        <v>527.7247696537621</v>
+        <v>527.72476965376211</v>
       </c>
       <c r="E10">
-        <v>501.4943966208947</v>
+        <v>501.49439662089469</v>
       </c>
       <c r="F10">
-        <v>490.0896333467724</v>
+        <v>490.08963334677242</v>
       </c>
       <c r="G10">
-        <v>489.3385328720651</v>
+        <v>489.33853287206512</v>
       </c>
       <c r="H10">
-        <v>490.0570675391879</v>
+        <v>490.05706753918793</v>
       </c>
       <c r="I10">
-        <v>485.2153021408902</v>
+        <v>485.21530214089017</v>
       </c>
       <c r="J10">
         <v>478.4077706099738</v>
       </c>
       <c r="K10">
-        <v>500.3343410937676</v>
+        <v>500.33434109376759</v>
       </c>
       <c r="L10">
-        <v>516.2745418351723</v>
+        <v>516.27454183517227</v>
       </c>
       <c r="M10">
-        <v>527.4213689572842</v>
+        <v>527.42136895728424</v>
       </c>
       <c r="N10">
-        <v>519.6658171209467</v>
+        <v>519.66581712094671</v>
       </c>
       <c r="O10">
-        <v>502.7907702276655</v>
+        <v>502.79077022766552</v>
       </c>
       <c r="P10">
-        <v>506.1946503987934</v>
+        <v>506.19465039879339</v>
       </c>
       <c r="Q10">
-        <v>509.6716751501243</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>509.67167515012432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
       </c>
       <c r="B11">
-        <v>536.2452002779759</v>
+        <v>536.24520027797587</v>
       </c>
       <c r="C11">
-        <v>564.6675206916237</v>
+        <v>564.66752069162374</v>
       </c>
       <c r="D11">
-        <v>528.3179669151136</v>
+        <v>528.31796691511363</v>
       </c>
       <c r="E11">
-        <v>500.6703229642018</v>
+        <v>500.67032296420177</v>
       </c>
       <c r="F11">
-        <v>490.3642970929668</v>
+        <v>490.36429709296681</v>
       </c>
       <c r="G11">
         <v>487.3979436442221</v>
       </c>
       <c r="H11">
-        <v>491.6774738175224</v>
+        <v>491.67747381752241</v>
       </c>
       <c r="I11">
         <v>485.380501234615</v>
       </c>
       <c r="J11">
-        <v>477.5889937284807</v>
+        <v>477.58899372848072</v>
       </c>
       <c r="K11">
-        <v>499.1911776968865</v>
+        <v>499.19117769688648</v>
       </c>
       <c r="L11">
-        <v>515.8813748513219</v>
+        <v>515.88137485132188</v>
       </c>
       <c r="M11">
-        <v>524.4289339312508</v>
+        <v>524.42893393125075</v>
       </c>
       <c r="N11">
-        <v>516.7184113928811</v>
+        <v>516.71841139288108</v>
       </c>
       <c r="O11">
-        <v>505.3893303750845</v>
+        <v>505.38933037508451</v>
       </c>
       <c r="P11">
-        <v>514.3996157706385</v>
+        <v>514.39961577063855</v>
       </c>
       <c r="Q11">
-        <v>506.9969097871038</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-        </is>
+        <v>506.99690978710379</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
       </c>
       <c r="B12">
         <v>510.0812827762598</v>
@@ -1007,111 +1183,107 @@
         <v>501.3742840778537</v>
       </c>
       <c r="E12">
-        <v>498.4154056588721</v>
+        <v>498.41540565887209</v>
       </c>
       <c r="F12">
-        <v>496.3786482430572</v>
+        <v>496.37864824305723</v>
       </c>
       <c r="G12">
         <v>490.7961644302739</v>
       </c>
       <c r="H12">
-        <v>488.5012782014019</v>
+        <v>488.50127820140187</v>
       </c>
       <c r="I12">
-        <v>489.1068818097984</v>
+        <v>489.10688180979838</v>
       </c>
       <c r="J12">
-        <v>495.3738097463769</v>
+        <v>495.37380974637688</v>
       </c>
       <c r="K12">
-        <v>503.0272340630706</v>
+        <v>503.02723406307058</v>
       </c>
       <c r="L12">
-        <v>514.0348259742005</v>
+        <v>514.03482597420054</v>
       </c>
       <c r="M12">
-        <v>529.6596840513099</v>
+        <v>529.65968405130991</v>
       </c>
       <c r="N12">
-        <v>544.0430284998617</v>
+        <v>544.04302849986175</v>
       </c>
       <c r="O12">
-        <v>549.5703586204124</v>
+        <v>549.57035862041243</v>
       </c>
       <c r="P12">
-        <v>557.8317290215194</v>
+        <v>557.83172902151944</v>
       </c>
       <c r="Q12">
-        <v>563.30331282891</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-        </is>
+        <v>563.30331282890995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>28</v>
       </c>
       <c r="B13">
-        <v>509.9842272781815</v>
+        <v>509.98422727818149</v>
       </c>
       <c r="C13">
         <v>507.485223692305</v>
       </c>
       <c r="D13">
-        <v>495.951867564343</v>
+        <v>495.95186756434299</v>
       </c>
       <c r="E13">
-        <v>488.0765395346352</v>
+        <v>488.07653953463517</v>
       </c>
       <c r="F13">
-        <v>485.3896729691892</v>
+        <v>485.38967296918918</v>
       </c>
       <c r="G13">
-        <v>490.5680421603898</v>
+        <v>490.56804216038978</v>
       </c>
       <c r="H13">
-        <v>494.1087277065297</v>
+        <v>494.10872770652969</v>
       </c>
       <c r="I13">
-        <v>495.3862047946466</v>
+        <v>495.38620479464657</v>
       </c>
       <c r="J13">
-        <v>505.6219160535159</v>
+        <v>505.62191605351592</v>
       </c>
       <c r="K13">
-        <v>512.1012440845925</v>
+        <v>512.10124408459251</v>
       </c>
       <c r="L13">
-        <v>528.0631678443241</v>
+        <v>528.06316784432408</v>
       </c>
       <c r="M13">
-        <v>534.3719602568005</v>
+        <v>534.37196025680055</v>
       </c>
       <c r="N13">
-        <v>538.7153845826405</v>
+        <v>538.71538458264047</v>
       </c>
       <c r="O13">
-        <v>544.0564745714468</v>
+        <v>544.05647457144676</v>
       </c>
       <c r="P13">
-        <v>552.5547090878825</v>
+        <v>552.55470908788254</v>
       </c>
       <c r="Q13">
-        <v>567.9736374236699</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>567.97363742366986</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
       </c>
       <c r="B14">
         <v>463.0950551255109</v>
       </c>
       <c r="C14">
-        <v>593.3032927128204</v>
+        <v>593.30329271282039</v>
       </c>
       <c r="D14">
         <v>516.398945182273</v>
@@ -1120,108 +1292,104 @@
         <v>472.7668528910869</v>
       </c>
       <c r="F14">
-        <v>447.009285378783</v>
+        <v>447.00928537878298</v>
       </c>
       <c r="G14">
         <v>435.2613696765182</v>
       </c>
       <c r="H14">
-        <v>427.7471266927489</v>
+        <v>427.74712669274891</v>
       </c>
       <c r="I14">
-        <v>437.2447194674208</v>
+        <v>437.24471946742079</v>
       </c>
       <c r="J14">
-        <v>442.9042014332722</v>
+        <v>442.90420143327219</v>
       </c>
       <c r="K14">
-        <v>450.8443665883397</v>
+        <v>450.84436658833971</v>
       </c>
       <c r="L14">
         <v>451.1290291878538</v>
       </c>
       <c r="M14">
-        <v>487.3407396755819</v>
+        <v>487.34073967558191</v>
       </c>
       <c r="N14">
-        <v>496.6777995550394</v>
+        <v>496.67779955503943</v>
       </c>
       <c r="O14">
         <v>490.9468779464604</v>
       </c>
       <c r="P14">
-        <v>489.2716186000877</v>
+        <v>489.27161860008772</v>
       </c>
       <c r="Q14">
-        <v>479.0499246737054</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>479.04992467370539</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
       </c>
       <c r="B15">
-        <v>463.6398442717277</v>
+        <v>463.63984427172772</v>
       </c>
       <c r="C15">
-        <v>594.122959924319</v>
+        <v>594.12295992431905</v>
       </c>
       <c r="D15">
-        <v>517.5804979752966</v>
+        <v>517.58049797529657</v>
       </c>
       <c r="E15">
         <v>472.7956289322762</v>
       </c>
       <c r="F15">
-        <v>446.1999361353766</v>
+        <v>446.19993613537662</v>
       </c>
       <c r="G15">
-        <v>434.7606650332764</v>
+        <v>434.76066503327638</v>
       </c>
       <c r="H15">
-        <v>427.7137342117848</v>
+        <v>427.71373421178481</v>
       </c>
       <c r="I15">
-        <v>436.7829838483397</v>
+        <v>436.78298384833971</v>
       </c>
       <c r="J15">
-        <v>442.9921923297238</v>
+        <v>442.99219232972382</v>
       </c>
       <c r="K15">
-        <v>450.7945742914168</v>
+        <v>450.79457429141678</v>
       </c>
       <c r="L15">
-        <v>451.2804179137281</v>
+        <v>451.28041791372812</v>
       </c>
       <c r="M15">
-        <v>485.6939857742528</v>
+        <v>485.69398577425278</v>
       </c>
       <c r="N15">
-        <v>496.0992738784627</v>
+        <v>496.09927387846272</v>
       </c>
       <c r="O15">
-        <v>493.4012914454141</v>
+        <v>493.40129144541407</v>
       </c>
       <c r="P15">
-        <v>492.655576436805</v>
+        <v>492.65557643680501</v>
       </c>
       <c r="Q15">
-        <v>482.0902467747092</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-        </is>
+        <v>482.09024677470921</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
       </c>
       <c r="B16">
-        <v>462.1886847233029</v>
+        <v>462.18868472330291</v>
       </c>
       <c r="C16">
-        <v>593.1069139943663</v>
+        <v>593.10691399436632</v>
       </c>
       <c r="D16">
         <v>515.5769610059931</v>
@@ -1230,245 +1398,237 @@
         <v>469.1481206011789</v>
       </c>
       <c r="F16">
-        <v>445.3862354784577</v>
+        <v>445.38623547845771</v>
       </c>
       <c r="G16">
-        <v>433.2067200939787</v>
+        <v>433.20672009397867</v>
       </c>
       <c r="H16">
-        <v>426.5986512862793</v>
+        <v>426.59865128627928</v>
       </c>
       <c r="I16">
-        <v>435.6689961217585</v>
+        <v>435.66899612175848</v>
       </c>
       <c r="J16">
-        <v>441.4743018628798</v>
+        <v>441.47430186287983</v>
       </c>
       <c r="K16">
-        <v>449.4405500369637</v>
+        <v>449.44055003696371</v>
       </c>
       <c r="L16">
         <v>450.5182709443813</v>
       </c>
       <c r="M16">
-        <v>484.1741733230394</v>
+        <v>484.17417332303938</v>
       </c>
       <c r="N16">
-        <v>493.0512834651562</v>
+        <v>493.05128346515619</v>
       </c>
       <c r="O16">
-        <v>491.2403212616903</v>
+        <v>491.24032126169033</v>
       </c>
       <c r="P16">
-        <v>491.540768082929</v>
+        <v>491.54076808292899</v>
       </c>
       <c r="Q16">
-        <v>483.5422132003865</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>483.54221320038653</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>32</v>
       </c>
       <c r="B17">
         <v>463.9003890237438</v>
       </c>
       <c r="C17">
-        <v>592.5162914209131</v>
+        <v>592.51629142091315</v>
       </c>
       <c r="D17">
-        <v>515.7325970277122</v>
+        <v>515.73259702771225</v>
       </c>
       <c r="E17">
-        <v>471.4666287928273</v>
+        <v>471.46662879282729</v>
       </c>
       <c r="F17">
-        <v>447.1780738284651</v>
+        <v>447.17807382846507</v>
       </c>
       <c r="G17">
-        <v>436.0834198489766</v>
+        <v>436.08341984897658</v>
       </c>
       <c r="H17">
-        <v>427.5892159832881</v>
+        <v>427.58921598328811</v>
       </c>
       <c r="I17">
-        <v>437.1342898690993</v>
+        <v>437.13428986909929</v>
       </c>
       <c r="J17">
-        <v>442.0946407510257</v>
+        <v>442.09464075102568</v>
       </c>
       <c r="K17">
-        <v>450.9861281447717</v>
+        <v>450.98612814477173</v>
       </c>
       <c r="L17">
-        <v>451.2387806653919</v>
+        <v>451.23878066539191</v>
       </c>
       <c r="M17">
-        <v>485.4331704785733</v>
+        <v>485.43317047857329</v>
       </c>
       <c r="N17">
-        <v>494.9578568024606</v>
+        <v>494.95785680246058</v>
       </c>
       <c r="O17">
-        <v>490.3175207559563</v>
+        <v>490.31752075595631</v>
       </c>
       <c r="P17">
         <v>487.4905088753265</v>
       </c>
       <c r="Q17">
-        <v>478.436110764063</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>478.43611076406302</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>33</v>
       </c>
       <c r="B18">
-        <v>510.5722950746252</v>
+        <v>510.57229507462517</v>
       </c>
       <c r="C18">
-        <v>505.1834548207428</v>
+        <v>505.18345482074278</v>
       </c>
       <c r="D18">
-        <v>501.3925252933832</v>
+        <v>501.39252529338319</v>
       </c>
       <c r="E18">
-        <v>498.5015227632863</v>
+        <v>498.50152276328629</v>
       </c>
       <c r="F18">
-        <v>496.792732548582</v>
+        <v>496.79273254858202</v>
       </c>
       <c r="G18">
-        <v>483.8516908709228</v>
+        <v>483.85169087092282</v>
       </c>
       <c r="H18">
-        <v>488.5617638736816</v>
+        <v>488.56176387368163</v>
       </c>
       <c r="I18">
-        <v>483.1436114739672</v>
+        <v>483.14361147396721</v>
       </c>
       <c r="J18">
-        <v>488.5845961999744</v>
+        <v>488.58459619997438</v>
       </c>
       <c r="K18">
-        <v>486.5288819094129</v>
+        <v>486.52888190941292</v>
       </c>
       <c r="L18">
-        <v>488.4342276695556</v>
+        <v>488.43422766955558</v>
       </c>
       <c r="M18">
-        <v>489.7910925737305</v>
+        <v>489.79109257373051</v>
       </c>
       <c r="N18">
-        <v>495.6620101035618</v>
+        <v>495.66201010356178</v>
       </c>
       <c r="O18">
-        <v>496.6067686872919</v>
+        <v>496.60676868729189</v>
       </c>
       <c r="P18">
-        <v>507.4395007334556</v>
+        <v>507.43950073345559</v>
       </c>
       <c r="Q18">
-        <v>506.7094546001962</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-        </is>
+        <v>506.70945460019618</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>34</v>
       </c>
       <c r="B19">
-        <v>509.2637996558196</v>
+        <v>509.26379965581958</v>
       </c>
       <c r="C19">
-        <v>504.6536803915191</v>
+        <v>504.65368039151912</v>
       </c>
       <c r="D19">
-        <v>498.6293493293773</v>
+        <v>498.62934932937731</v>
       </c>
       <c r="E19">
-        <v>494.8970066195087</v>
+        <v>494.89700661950872</v>
       </c>
       <c r="F19">
-        <v>499.7683970267179</v>
+        <v>499.76839702671788</v>
       </c>
       <c r="G19">
-        <v>484.2650920871733</v>
+        <v>484.26509208717329</v>
       </c>
       <c r="H19">
-        <v>490.7124297112373</v>
+        <v>490.71242971123729</v>
       </c>
       <c r="I19">
-        <v>485.0345020551611</v>
+        <v>485.03450205516111</v>
       </c>
       <c r="J19">
-        <v>484.3712564551629</v>
+        <v>484.37125645516289</v>
       </c>
       <c r="K19">
         <v>487.0281615471024</v>
       </c>
       <c r="L19">
-        <v>479.5999388745852</v>
+        <v>479.59993887458518</v>
       </c>
       <c r="M19">
-        <v>494.5294377696642</v>
+        <v>494.52943776966418</v>
       </c>
       <c r="N19">
-        <v>501.9514728151217</v>
+        <v>501.95147281512169</v>
       </c>
       <c r="O19">
-        <v>506.7854637441642</v>
+        <v>506.78546374416419</v>
       </c>
       <c r="P19">
-        <v>508.7100237228032</v>
+        <v>508.71002372280321</v>
       </c>
       <c r="Q19">
-        <v>505.4531018705297</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>505.45310187052968</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
       </c>
       <c r="B20">
-        <v>510.1312090210045</v>
+        <v>510.13120902100451</v>
       </c>
       <c r="C20">
-        <v>503.9539557384013</v>
+        <v>503.95395573840131</v>
       </c>
       <c r="D20">
-        <v>497.2184112804293</v>
+        <v>497.21841128042928</v>
       </c>
       <c r="E20">
-        <v>488.6040236274461</v>
+        <v>488.60402362744611</v>
       </c>
       <c r="F20">
-        <v>496.2721502421201</v>
+        <v>496.27215024212012</v>
       </c>
       <c r="G20">
-        <v>490.5248765234469</v>
+        <v>490.52487652344689</v>
       </c>
       <c r="H20">
-        <v>479.8727424217039</v>
+        <v>479.87274242170389</v>
       </c>
       <c r="I20">
         <v>476.8904152818252</v>
       </c>
       <c r="J20">
-        <v>477.5331961552448</v>
+        <v>477.53319615524481</v>
       </c>
       <c r="K20">
-        <v>478.7416961431895</v>
+        <v>478.74169614318947</v>
       </c>
       <c r="L20">
-        <v>479.9017742591761</v>
+        <v>479.90177425917608</v>
       </c>
       <c r="M20">
         <v>489.1619874442664</v>
@@ -1477,209 +1637,201 @@
         <v>502.4036768187168</v>
       </c>
       <c r="O20">
-        <v>507.9064896775241</v>
+        <v>507.90648967752412</v>
       </c>
       <c r="P20">
-        <v>495.3211164393304</v>
+        <v>495.32111643933041</v>
       </c>
       <c r="Q20">
-        <v>494.9715647356608</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>494.97156473566082</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
       </c>
       <c r="B21">
-        <v>517.7090004271305</v>
+        <v>517.70900042713049</v>
       </c>
       <c r="C21">
-        <v>564.061073358961</v>
+        <v>564.06107335896104</v>
       </c>
       <c r="D21">
-        <v>508.9571839235317</v>
+        <v>508.95718392353172</v>
       </c>
       <c r="E21">
-        <v>505.7610568741471</v>
+        <v>505.76105687414707</v>
       </c>
       <c r="F21">
-        <v>498.8788407269614</v>
+        <v>498.87884072696141</v>
       </c>
       <c r="G21">
-        <v>500.7279350810771</v>
+        <v>500.72793508107708</v>
       </c>
       <c r="H21">
-        <v>508.3474971651714</v>
+        <v>508.34749716517138</v>
       </c>
       <c r="I21">
-        <v>542.5561395793322</v>
+        <v>542.55613957933224</v>
       </c>
       <c r="J21">
-        <v>552.4600693067599</v>
+        <v>552.46006930675992</v>
       </c>
       <c r="K21">
-        <v>552.3292787878602</v>
+        <v>552.32927878786018</v>
       </c>
       <c r="L21">
         <v>564.322546065496</v>
       </c>
       <c r="M21">
-        <v>577.5481025995343</v>
+        <v>577.54810259953433</v>
       </c>
       <c r="N21">
-        <v>594.9193486480164</v>
+        <v>594.91934864801635</v>
       </c>
       <c r="O21">
-        <v>613.9242417126466</v>
+        <v>613.92424171264656</v>
       </c>
       <c r="P21">
-        <v>637.0402936221527</v>
+        <v>637.04029362215272</v>
       </c>
       <c r="Q21">
-        <v>664.8160840327375</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>664.81608403273754</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>37</v>
       </c>
       <c r="B22">
         <v>515.9863874956385</v>
       </c>
       <c r="C22">
-        <v>565.0541247300683</v>
+        <v>565.05412473006834</v>
       </c>
       <c r="D22">
-        <v>509.9232444244432</v>
+        <v>509.92324442444323</v>
       </c>
       <c r="E22">
-        <v>506.0392324598864</v>
+        <v>506.03923245988642</v>
       </c>
       <c r="F22">
-        <v>498.6272799450392</v>
+        <v>498.62727994503922</v>
       </c>
       <c r="G22">
-        <v>497.2532124477852</v>
+        <v>497.25321244778519</v>
       </c>
       <c r="H22">
-        <v>495.6812193952441</v>
+        <v>495.68121939524411</v>
       </c>
       <c r="I22">
-        <v>530.053805284978</v>
+        <v>530.05380528497801</v>
       </c>
       <c r="J22">
         <v>546.4362217332075</v>
       </c>
       <c r="K22">
-        <v>544.3304031774749</v>
+        <v>544.33040317747486</v>
       </c>
       <c r="L22">
-        <v>554.1635319623207</v>
+        <v>554.16353196232069</v>
       </c>
       <c r="M22">
-        <v>569.3212755814546</v>
+        <v>569.32127558145464</v>
       </c>
       <c r="N22">
-        <v>587.5518307923113</v>
+        <v>587.55183079231131</v>
       </c>
       <c r="O22">
         <v>602.930661599725</v>
       </c>
       <c r="P22">
-        <v>625.1238458882481</v>
+        <v>625.12384588824807</v>
       </c>
       <c r="Q22">
-        <v>647.2175863133178</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>647.21758631331784</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>38</v>
       </c>
       <c r="B23">
-        <v>507.2368023108145</v>
+        <v>507.23680231081448</v>
       </c>
       <c r="C23">
-        <v>506.9854965407283</v>
+        <v>506.98549654072832</v>
       </c>
       <c r="D23">
-        <v>516.7302122918495</v>
+        <v>516.73021229184951</v>
       </c>
       <c r="E23">
-        <v>507.9969748819198</v>
+        <v>507.99697488191981</v>
       </c>
       <c r="F23">
-        <v>500.1866382662568</v>
+        <v>500.18663826625681</v>
       </c>
       <c r="G23">
-        <v>524.0583363193925</v>
+        <v>524.05833631939254</v>
       </c>
       <c r="H23">
-        <v>559.9441933939967</v>
+        <v>559.94419339399667</v>
       </c>
       <c r="I23">
-        <v>590.9671201283861</v>
+        <v>590.96712012838611</v>
       </c>
       <c r="J23">
-        <v>593.6317335166485</v>
+        <v>593.63173351664852</v>
       </c>
       <c r="K23">
-        <v>614.6680139690307</v>
+        <v>614.66801396903065</v>
       </c>
       <c r="L23">
-        <v>626.7235979907488</v>
+        <v>626.72359799074877</v>
       </c>
       <c r="M23">
-        <v>647.1095809175854</v>
+        <v>647.10958091758539</v>
       </c>
       <c r="N23">
-        <v>654.8065552338878</v>
+        <v>654.80655523388782</v>
       </c>
       <c r="O23">
-        <v>675.9655001633989</v>
+        <v>675.96550016339893</v>
       </c>
       <c r="P23">
-        <v>691.9060500688232</v>
+        <v>691.90605006882322</v>
       </c>
       <c r="Q23">
-        <v>713.6929816630314</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>713.69298166303145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>39</v>
       </c>
       <c r="B24">
-        <v>716.7981918528357</v>
+        <v>716.79819185283566</v>
       </c>
       <c r="C24">
-        <v>716.7981918528357</v>
+        <v>716.79819185283566</v>
       </c>
       <c r="D24">
-        <v>738.513396437601</v>
+        <v>738.51339643760105</v>
       </c>
       <c r="E24">
-        <v>728.8456549171243</v>
+        <v>728.84565491712431</v>
       </c>
       <c r="F24">
-        <v>763.6836194017478</v>
+        <v>763.68361940174782</v>
       </c>
       <c r="G24">
-        <v>866.7222281331506</v>
+        <v>866.72222813315057</v>
       </c>
       <c r="H24">
-        <v>827.1608232825149</v>
+        <v>827.16082328251491</v>
       </c>
       <c r="I24">
-        <v>847.2590503843725</v>
+        <v>847.25905038437247</v>
       </c>
       <c r="J24">
         <v>867.0342701071919</v>
@@ -1688,29 +1840,27 @@
         <v>891.7997214528599</v>
       </c>
       <c r="L24">
-        <v>905.0971140452709</v>
+        <v>905.09711404527093</v>
       </c>
       <c r="M24">
-        <v>918.7302310423759</v>
+        <v>918.73023104237586</v>
       </c>
       <c r="N24">
-        <v>914.9899445805843</v>
+        <v>914.98994458058428</v>
       </c>
       <c r="O24">
-        <v>913.3116160084674</v>
+        <v>913.31161600846735</v>
       </c>
       <c r="P24">
-        <v>920.1056484043273</v>
+        <v>920.10564840432733</v>
       </c>
       <c r="Q24">
-        <v>925.9870178540514</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>925.98701785405137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>40</v>
       </c>
       <c r="B25">
         <v>726.2555492366796</v>
@@ -1719,19 +1869,19 @@
         <v>726.2555492366796</v>
       </c>
       <c r="D25">
-        <v>741.7012414261421</v>
+        <v>741.70124142614213</v>
       </c>
       <c r="E25">
-        <v>755.6383566936167</v>
+        <v>755.63835669361674</v>
       </c>
       <c r="F25">
-        <v>786.5951263095446</v>
+        <v>786.59512630954464</v>
       </c>
       <c r="G25">
         <v>811.1082209835314</v>
       </c>
       <c r="H25">
-        <v>860.8704133612709</v>
+        <v>860.87041336127095</v>
       </c>
       <c r="I25">
         <v>899.0400567244476</v>
@@ -1740,19 +1890,19 @@
         <v>926.5176348352544</v>
       </c>
       <c r="K25">
-        <v>938.0418130365701</v>
+        <v>938.04181303657015</v>
       </c>
       <c r="L25">
         <v>942.0056548167704</v>
       </c>
       <c r="M25">
-        <v>965.4853152372244</v>
+        <v>965.48531523722443</v>
       </c>
       <c r="N25">
-        <v>988.1891767353734</v>
+        <v>988.18917673537339</v>
       </c>
       <c r="O25">
-        <v>1005.59903627795</v>
+        <v>1005.5990362779499</v>
       </c>
       <c r="P25">
         <v>1013.708178225481</v>
@@ -1761,75 +1911,71 @@
         <v>1020.709337425577</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>41</v>
       </c>
       <c r="B26">
-        <v>723.6023682642518</v>
+        <v>723.60236826425182</v>
       </c>
       <c r="C26">
-        <v>723.6023682642517</v>
+        <v>723.60236826425171</v>
       </c>
       <c r="D26">
-        <v>736.373644419278</v>
+        <v>736.37364441927798</v>
       </c>
       <c r="E26">
-        <v>734.7260609953826</v>
+        <v>734.72606099538257</v>
       </c>
       <c r="F26">
-        <v>759.9946842025112</v>
+        <v>759.99468420251117</v>
       </c>
       <c r="G26">
-        <v>795.0653985010746</v>
+        <v>795.06539850107458</v>
       </c>
       <c r="H26">
-        <v>802.1287871366302</v>
+        <v>802.12878713663019</v>
       </c>
       <c r="I26">
-        <v>829.0234568065191</v>
+        <v>829.02345680651911</v>
       </c>
       <c r="J26">
-        <v>822.2333780996532</v>
+        <v>822.23337809965324</v>
       </c>
       <c r="K26">
-        <v>801.5061019838336</v>
+        <v>801.50610198383356</v>
       </c>
       <c r="L26">
-        <v>781.8075225193514</v>
+        <v>781.80752251935144</v>
       </c>
       <c r="M26">
-        <v>837.157433143473</v>
+        <v>837.15743314347299</v>
       </c>
       <c r="N26">
-        <v>884.0158499065503</v>
+        <v>884.01584990655033</v>
       </c>
       <c r="O26">
-        <v>867.9757460330516</v>
+        <v>867.97574603305156</v>
       </c>
       <c r="P26">
-        <v>875.9514520737547</v>
+        <v>875.95145207375469</v>
       </c>
       <c r="Q26">
-        <v>879.0788250014039</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>879.07882500140386</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>42</v>
       </c>
       <c r="B27">
-        <v>731.1475180843846</v>
+        <v>731.14751808438461</v>
       </c>
       <c r="C27">
-        <v>729.6642460537016</v>
+        <v>729.66424605370162</v>
       </c>
       <c r="D27">
-        <v>735.6794084870689</v>
+        <v>735.67940848706894</v>
       </c>
       <c r="E27">
         <v>774.9149750811406</v>
@@ -1838,1140 +1984,1113 @@
         <v>755.4041814496843</v>
       </c>
       <c r="G27">
-        <v>796.7862852671296</v>
+        <v>796.78628526712964</v>
       </c>
       <c r="H27">
         <v>794.3378486799686</v>
       </c>
       <c r="I27">
-        <v>770.5569023535653</v>
+        <v>770.55690235356531</v>
       </c>
       <c r="J27">
         <v>767.9589927130861</v>
       </c>
       <c r="K27">
-        <v>797.4993023971663</v>
+        <v>797.49930239716628</v>
       </c>
       <c r="L27">
-        <v>826.7667195115393</v>
+        <v>826.76671951153935</v>
       </c>
       <c r="M27">
-        <v>849.4867880240221</v>
+        <v>849.48678802402208</v>
       </c>
       <c r="N27">
-        <v>875.6835309861576</v>
+        <v>875.68353098615762</v>
       </c>
       <c r="O27">
-        <v>852.2774320798924</v>
+        <v>852.27743207989238</v>
       </c>
       <c r="P27">
         <v>885.8326949892587</v>
       </c>
       <c r="Q27">
-        <v>900.1882864637288</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>900.18828646372879</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>43</v>
       </c>
       <c r="B28">
-        <v>456.7670234273207</v>
+        <v>456.76702342732068</v>
       </c>
       <c r="C28">
-        <v>494.1718324879466</v>
+        <v>494.17183248794657</v>
       </c>
       <c r="D28">
-        <v>457.2726608478093</v>
+        <v>457.27266084780928</v>
       </c>
       <c r="E28">
-        <v>436.548426692727</v>
+        <v>436.54842669272699</v>
       </c>
       <c r="F28">
-        <v>422.0525576478361</v>
+        <v>422.05255764783612</v>
       </c>
       <c r="G28">
-        <v>435.546475900848</v>
+        <v>435.54647590084801</v>
       </c>
       <c r="H28">
-        <v>438.4193524878021</v>
+        <v>438.41935248780209</v>
       </c>
       <c r="I28">
-        <v>439.073499646814</v>
+        <v>439.07349964681401</v>
       </c>
       <c r="J28">
-        <v>450.3089028085031</v>
+        <v>450.30890280850309</v>
       </c>
       <c r="K28">
-        <v>436.9194014568419</v>
+        <v>436.91940145684191</v>
       </c>
       <c r="L28">
         <v>431.0416989452325</v>
       </c>
       <c r="M28">
-        <v>440.0308784727205</v>
+        <v>440.03087847272047</v>
       </c>
       <c r="N28">
-        <v>457.4481167298413</v>
+        <v>457.44811672984127</v>
       </c>
       <c r="O28">
-        <v>474.9185643220677</v>
+        <v>474.91856432206771</v>
       </c>
       <c r="P28">
-        <v>486.6751551859794</v>
+        <v>486.67515518597941</v>
       </c>
       <c r="Q28">
-        <v>507.3380416193929</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>507.33804161939292</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>44</v>
       </c>
       <c r="B29">
         <v>420.7687677324667</v>
       </c>
       <c r="C29">
-        <v>493.7716594694309</v>
+        <v>493.77165946943092</v>
       </c>
       <c r="D29">
-        <v>454.6222737153017</v>
+        <v>454.62227371530167</v>
       </c>
       <c r="E29">
-        <v>427.3212037087227</v>
+        <v>427.32120370872269</v>
       </c>
       <c r="F29">
-        <v>405.3556884938725</v>
+        <v>405.35568849387249</v>
       </c>
       <c r="G29">
         <v>410.8258621617735</v>
       </c>
       <c r="H29">
-        <v>401.930015852066</v>
+        <v>401.93001585206599</v>
       </c>
       <c r="I29">
-        <v>405.6414535362306</v>
+        <v>405.64145353623059</v>
       </c>
       <c r="J29">
-        <v>415.3786542118316</v>
+        <v>415.37865421183159</v>
       </c>
       <c r="K29">
-        <v>390.6250340272493</v>
+        <v>390.62503402724928</v>
       </c>
       <c r="L29">
-        <v>387.9745899634069</v>
+        <v>387.97458996340691</v>
       </c>
       <c r="M29">
-        <v>387.3108943950307</v>
+        <v>387.31089439503069</v>
       </c>
       <c r="N29">
-        <v>400.7565836826702</v>
+        <v>400.75658368267023</v>
       </c>
       <c r="O29">
-        <v>410.7597665156169</v>
+        <v>410.75976651561689</v>
       </c>
       <c r="P29">
-        <v>426.7326610257837</v>
+        <v>426.73266102578373</v>
       </c>
       <c r="Q29">
-        <v>445.0785122153284</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>445.07851221532837</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>45</v>
       </c>
       <c r="B30">
         <v>465.6684750894326</v>
       </c>
       <c r="C30">
-        <v>485.1286828287267</v>
+        <v>485.12868282872671</v>
       </c>
       <c r="D30">
-        <v>465.8777975436603</v>
+        <v>465.87779754366028</v>
       </c>
       <c r="E30">
         <v>444.11467723171</v>
       </c>
       <c r="F30">
-        <v>424.7934237313203</v>
+        <v>424.79342373132027</v>
       </c>
       <c r="G30">
-        <v>436.6077076042398</v>
+        <v>436.60770760423981</v>
       </c>
       <c r="H30">
-        <v>425.7726142799717</v>
+        <v>425.77261427997172</v>
       </c>
       <c r="I30">
-        <v>428.0737264649139</v>
+        <v>428.07372646491388</v>
       </c>
       <c r="J30">
-        <v>428.5549984426428</v>
+        <v>428.55499844264278</v>
       </c>
       <c r="K30">
-        <v>429.6077096132627</v>
+        <v>429.60770961326273</v>
       </c>
       <c r="L30">
-        <v>421.2749491121567</v>
+        <v>421.27494911215672</v>
       </c>
       <c r="M30">
-        <v>425.4643062135908</v>
+        <v>425.46430621359082</v>
       </c>
       <c r="N30">
-        <v>429.7971423517217</v>
+        <v>429.79714235172167</v>
       </c>
       <c r="O30">
-        <v>444.1414764433637</v>
+        <v>444.14147644336367</v>
       </c>
       <c r="P30">
-        <v>460.8537088842233</v>
+        <v>460.85370888422329</v>
       </c>
       <c r="Q30">
-        <v>479.4335845142106</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>479.43358451421062</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>46</v>
       </c>
       <c r="B31">
-        <v>475.9220783447159</v>
+        <v>475.92207834471589</v>
       </c>
       <c r="C31">
-        <v>483.4742988250377</v>
+        <v>483.47429882503769</v>
       </c>
       <c r="D31">
-        <v>464.2925934893084</v>
+        <v>464.29259348930839</v>
       </c>
       <c r="E31">
-        <v>442.2323311547015</v>
+        <v>442.23233115470151</v>
       </c>
       <c r="F31">
-        <v>423.3705658177192</v>
+        <v>423.37056581771918</v>
       </c>
       <c r="G31">
-        <v>434.6779996282722</v>
+        <v>434.67799962827218</v>
       </c>
       <c r="H31">
-        <v>424.8420034767711</v>
+        <v>424.84200347677108</v>
       </c>
       <c r="I31">
-        <v>427.1634139129123</v>
+        <v>427.16341391291229</v>
       </c>
       <c r="J31">
-        <v>430.4027042605479</v>
+        <v>430.40270426054792</v>
       </c>
       <c r="K31">
-        <v>435.9686197612066</v>
+        <v>435.96861976120658</v>
       </c>
       <c r="L31">
         <v>432.8586854416526</v>
       </c>
       <c r="M31">
-        <v>434.6237734959672</v>
+        <v>434.62377349596721</v>
       </c>
       <c r="N31">
-        <v>436.1490312676912</v>
+        <v>436.14903126769121</v>
       </c>
       <c r="O31">
-        <v>447.7638445335139</v>
+        <v>447.76384453351392</v>
       </c>
       <c r="P31">
-        <v>459.5685167798151</v>
+        <v>459.56851677981513</v>
       </c>
       <c r="Q31">
-        <v>454.8942334451559</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-        </is>
+        <v>454.89423344515592</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>47</v>
       </c>
       <c r="B32">
-        <v>427.093812096267</v>
+        <v>427.09381209626702</v>
       </c>
       <c r="C32">
-        <v>494.3730527239505</v>
+        <v>494.37305272395048</v>
       </c>
       <c r="D32">
-        <v>455.0862417149676</v>
+        <v>455.08624171496763</v>
       </c>
       <c r="E32">
-        <v>428.5901252707822</v>
+        <v>428.59012527078221</v>
       </c>
       <c r="F32">
-        <v>407.4033724966134</v>
+        <v>407.40337249661337</v>
       </c>
       <c r="G32">
-        <v>412.1610605522383</v>
+        <v>412.16106055223833</v>
       </c>
       <c r="H32">
-        <v>405.9889178036619</v>
+        <v>405.98891780366188</v>
       </c>
       <c r="I32">
-        <v>407.7229990294082</v>
+        <v>407.72299902940819</v>
       </c>
       <c r="J32">
-        <v>423.4731034521071</v>
+        <v>423.47310345210713</v>
       </c>
       <c r="K32">
-        <v>404.908420018618</v>
+        <v>404.90842001861802</v>
       </c>
       <c r="L32">
-        <v>396.8434885683506</v>
+        <v>396.84348856835061</v>
       </c>
       <c r="M32">
         <v>390.013436851584</v>
       </c>
       <c r="N32">
-        <v>397.692396612017</v>
+        <v>397.69239661201698</v>
       </c>
       <c r="O32">
         <v>404.180863404148</v>
       </c>
       <c r="P32">
-        <v>412.8564463428999</v>
+        <v>412.85644634289991</v>
       </c>
       <c r="Q32">
-        <v>437.7083285139213</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-        </is>
+        <v>437.70832851392129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>48</v>
       </c>
       <c r="B33">
-        <v>428.8773711220384</v>
+        <v>428.87737112203843</v>
       </c>
       <c r="C33">
-        <v>495.6784996533373</v>
+        <v>495.67849965333733</v>
       </c>
       <c r="D33">
-        <v>456.8755658180851</v>
+        <v>456.87556581808508</v>
       </c>
       <c r="E33">
-        <v>428.8696898862012</v>
+        <v>428.86968988620117</v>
       </c>
       <c r="F33">
-        <v>407.5818034075612</v>
+        <v>407.58180340756121</v>
       </c>
       <c r="G33">
-        <v>410.6330034228292</v>
+        <v>410.63300342282918</v>
       </c>
       <c r="H33">
-        <v>404.4124578313565</v>
+        <v>404.41245783135651</v>
       </c>
       <c r="I33">
-        <v>406.2227823259414</v>
+        <v>406.22278232594141</v>
       </c>
       <c r="J33">
-        <v>421.8774348911257</v>
+        <v>421.87743489112569</v>
       </c>
       <c r="K33">
-        <v>402.5092076887045</v>
+        <v>402.50920768870452</v>
       </c>
       <c r="L33">
-        <v>395.553520718376</v>
+        <v>395.55352071837598</v>
       </c>
       <c r="M33">
         <v>390.7406805766098</v>
       </c>
       <c r="N33">
-        <v>399.3145583774469</v>
+        <v>399.31455837744687</v>
       </c>
       <c r="O33">
-        <v>405.3444381908564</v>
+        <v>405.34443819085641</v>
       </c>
       <c r="P33">
-        <v>417.3056589955083</v>
+        <v>417.30565899550828</v>
       </c>
       <c r="Q33">
-        <v>445.8572516752293</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-        </is>
+        <v>445.85725167522929</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>49</v>
       </c>
       <c r="B34">
         <v>432.043565396247</v>
       </c>
       <c r="C34">
-        <v>494.6792341244569</v>
+        <v>494.67923412445691</v>
       </c>
       <c r="D34">
         <v>455.5573190231155</v>
       </c>
       <c r="E34">
-        <v>428.3036182867528</v>
+        <v>428.30361828675279</v>
       </c>
       <c r="F34">
-        <v>406.744683897401</v>
+        <v>406.74468389740099</v>
       </c>
       <c r="G34">
-        <v>411.4353883520001</v>
+        <v>411.43538835200007</v>
       </c>
       <c r="H34">
-        <v>405.5457477179089</v>
+        <v>405.54574771790891</v>
       </c>
       <c r="I34">
-        <v>407.2863765255547</v>
+        <v>407.28637652555472</v>
       </c>
       <c r="J34">
-        <v>426.7732242643581</v>
+        <v>426.77322426435808</v>
       </c>
       <c r="K34">
-        <v>405.426151643555</v>
+        <v>405.42615164355499</v>
       </c>
       <c r="L34">
-        <v>397.8999825417361</v>
+        <v>397.89998254173611</v>
       </c>
       <c r="M34">
-        <v>390.6337312145349</v>
+        <v>390.63373121453492</v>
       </c>
       <c r="N34">
-        <v>399.4359054456332</v>
+        <v>399.43590544563318</v>
       </c>
       <c r="O34">
-        <v>405.4361265594468</v>
+        <v>405.43612655944679</v>
       </c>
       <c r="P34">
-        <v>414.0271124741276</v>
+        <v>414.02711247412759</v>
       </c>
       <c r="Q34">
-        <v>440.7237819660226</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-        </is>
+        <v>440.72378196602261</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>50</v>
       </c>
       <c r="B35">
-        <v>426.2516865146533</v>
+        <v>426.25168651465327</v>
       </c>
       <c r="C35">
-        <v>495.6506242352875</v>
+        <v>495.65062423528752</v>
       </c>
       <c r="D35">
-        <v>456.4115184236883</v>
+        <v>456.41151842368828</v>
       </c>
       <c r="E35">
-        <v>429.1080133682619</v>
+        <v>429.10801336826188</v>
       </c>
       <c r="F35">
-        <v>406.6369613021153</v>
+        <v>406.63696130211531</v>
       </c>
       <c r="G35">
         <v>410.4172225671611</v>
       </c>
       <c r="H35">
-        <v>405.0082027979057</v>
+        <v>405.00820279790571</v>
       </c>
       <c r="I35">
-        <v>407.3336202385563</v>
+        <v>407.33362023855631</v>
       </c>
       <c r="J35">
-        <v>425.8496611137911</v>
+        <v>425.84966111379111</v>
       </c>
       <c r="K35">
-        <v>406.4188873648681</v>
+        <v>406.41888736486811</v>
       </c>
       <c r="L35">
-        <v>398.1153575339698</v>
+        <v>398.11535753396981</v>
       </c>
       <c r="M35">
-        <v>387.777426050567</v>
+        <v>387.77742605056699</v>
       </c>
       <c r="N35">
         <v>397.3212467026388</v>
       </c>
       <c r="O35">
-        <v>402.9132184171069</v>
+        <v>402.91321841710692</v>
       </c>
       <c r="P35">
         <v>409.6044598621292</v>
       </c>
       <c r="Q35">
-        <v>432.5745842330666</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>432.57458423306662</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>51</v>
       </c>
       <c r="B36">
-        <v>428.5207568858809</v>
+        <v>428.52075688588093</v>
       </c>
       <c r="C36">
-        <v>494.6322721052455</v>
+        <v>494.63227210524548</v>
       </c>
       <c r="D36">
-        <v>455.5051558013425</v>
+        <v>455.50515580134248</v>
       </c>
       <c r="E36">
-        <v>427.3228523103074</v>
+        <v>427.32285231030738</v>
       </c>
       <c r="F36">
-        <v>406.0654211833552</v>
+        <v>406.06542118335523</v>
       </c>
       <c r="G36">
-        <v>411.1789078466454</v>
+        <v>411.17890784664542</v>
       </c>
       <c r="H36">
-        <v>403.7764966919469</v>
+        <v>403.77649669194687</v>
       </c>
       <c r="I36">
-        <v>407.8820819298293</v>
+        <v>407.88208192982933</v>
       </c>
       <c r="J36">
-        <v>423.6496075297572</v>
+        <v>423.64960752975719</v>
       </c>
       <c r="K36">
-        <v>403.4926746042836</v>
+        <v>403.49267460428359</v>
       </c>
       <c r="L36">
         <v>397.3160384577622</v>
       </c>
       <c r="M36">
-        <v>395.6632544207188</v>
+        <v>395.66325442071877</v>
       </c>
       <c r="N36">
-        <v>404.8743730158333</v>
+        <v>404.87437301583333</v>
       </c>
       <c r="O36">
-        <v>411.4175095589026</v>
+        <v>411.41750955890262</v>
       </c>
       <c r="P36">
-        <v>420.4960013823649</v>
+        <v>420.49600138236491</v>
       </c>
       <c r="Q36">
-        <v>440.2021697966114</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-        </is>
+        <v>440.20216979661137</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>52</v>
       </c>
       <c r="B37">
-        <v>432.7208570348744</v>
+        <v>432.72085703487443</v>
       </c>
       <c r="C37">
-        <v>496.4585889260991</v>
+        <v>496.45858892609908</v>
       </c>
       <c r="D37">
         <v>457.0392675820936</v>
       </c>
       <c r="E37">
-        <v>429.5459313685068</v>
+        <v>429.54593136850679</v>
       </c>
       <c r="F37">
-        <v>407.890642128277</v>
+        <v>407.89064212827702</v>
       </c>
       <c r="G37">
-        <v>413.0840696279221</v>
+        <v>413.08406962792208</v>
       </c>
       <c r="H37">
-        <v>407.4240799112501</v>
+        <v>407.42407991125009</v>
       </c>
       <c r="I37">
-        <v>410.4417521147525</v>
+        <v>410.44175211475249</v>
       </c>
       <c r="J37">
-        <v>423.8060734828014</v>
+        <v>423.80607348280142</v>
       </c>
       <c r="K37">
         <v>404.4407173088054</v>
       </c>
       <c r="L37">
-        <v>401.3283808582436</v>
+        <v>401.32838085824358</v>
       </c>
       <c r="M37">
-        <v>396.1801163831707</v>
+        <v>396.18011638317068</v>
       </c>
       <c r="N37">
-        <v>404.5444287713804</v>
+        <v>404.54442877138041</v>
       </c>
       <c r="O37">
-        <v>410.0473253697103</v>
+        <v>410.04732536971028</v>
       </c>
       <c r="P37">
-        <v>418.4864296050429</v>
+        <v>418.48642960504287</v>
       </c>
       <c r="Q37">
-        <v>440.7496443184963</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-        </is>
+        <v>440.74964431849628</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>53</v>
       </c>
       <c r="B38">
-        <v>428.0640766952931</v>
+        <v>428.06407669529312</v>
       </c>
       <c r="C38">
-        <v>494.7401279538886</v>
+        <v>494.74012795388859</v>
       </c>
       <c r="D38">
-        <v>455.7127114078572</v>
+        <v>455.71271140785723</v>
       </c>
       <c r="E38">
-        <v>427.9010780488051</v>
+        <v>427.90107804880512</v>
       </c>
       <c r="F38">
         <v>406.2643978043929</v>
       </c>
       <c r="G38">
-        <v>410.4522997667455</v>
+        <v>410.45229976674551</v>
       </c>
       <c r="H38">
-        <v>403.2486816696768</v>
+        <v>403.24868166967678</v>
       </c>
       <c r="I38">
-        <v>407.833152040955</v>
+        <v>407.83315204095499</v>
       </c>
       <c r="J38">
-        <v>420.2438722471807</v>
+        <v>420.24387224718072</v>
       </c>
       <c r="K38">
-        <v>402.0241297832292</v>
+        <v>402.02412978322923</v>
       </c>
       <c r="L38">
-        <v>396.6192551635767</v>
+        <v>396.61925516357672</v>
       </c>
       <c r="M38">
-        <v>392.4887103768634</v>
+        <v>392.48871037686342</v>
       </c>
       <c r="N38">
-        <v>399.2176185300426</v>
+        <v>399.21761853004261</v>
       </c>
       <c r="O38">
-        <v>406.2421242042204</v>
+        <v>406.24212420422037</v>
       </c>
       <c r="P38">
-        <v>415.3397657365811</v>
+        <v>415.33976573658111</v>
       </c>
       <c r="Q38">
-        <v>438.8799075619406</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>438.87990756194063</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>54</v>
       </c>
       <c r="B39">
-        <v>427.8445127201852</v>
+        <v>427.84451272018521</v>
       </c>
       <c r="C39">
-        <v>495.4738155207637</v>
+        <v>495.47381552076371</v>
       </c>
       <c r="D39">
         <v>456.7496963900864</v>
       </c>
       <c r="E39">
-        <v>429.8764073941018</v>
+        <v>429.87640739410182</v>
       </c>
       <c r="F39">
         <v>407.3478062416811</v>
       </c>
       <c r="G39">
-        <v>412.3226765393231</v>
+        <v>412.32267653932308</v>
       </c>
       <c r="H39">
-        <v>406.6993083904005</v>
+        <v>406.69930839040052</v>
       </c>
       <c r="I39">
-        <v>408.8164185041878</v>
+        <v>408.81641850418782</v>
       </c>
       <c r="J39">
-        <v>424.8672584615181</v>
+        <v>424.86725846151808</v>
       </c>
       <c r="K39">
-        <v>405.3851449982712</v>
+        <v>405.38514499827119</v>
       </c>
       <c r="L39">
-        <v>398.8299476445104</v>
+        <v>398.82994764451041</v>
       </c>
       <c r="M39">
-        <v>393.9045388540338</v>
+        <v>393.90453885403377</v>
       </c>
       <c r="N39">
         <v>401.8789883840949</v>
       </c>
       <c r="O39">
-        <v>407.8147626075734</v>
+        <v>407.81476260757341</v>
       </c>
       <c r="P39">
-        <v>413.8397052557995</v>
+        <v>413.83970525579952</v>
       </c>
       <c r="Q39">
-        <v>436.8471503037725</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>436.84715030377248</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>55</v>
       </c>
       <c r="B40">
-        <v>425.6894503394076</v>
+        <v>425.68945033940759</v>
       </c>
       <c r="C40">
-        <v>495.5064018813732</v>
+        <v>495.50640188137322</v>
       </c>
       <c r="D40">
-        <v>455.662208145316</v>
+        <v>455.66220814531601</v>
       </c>
       <c r="E40">
-        <v>427.4881056019987</v>
+        <v>427.48810560199871</v>
       </c>
       <c r="F40">
-        <v>405.8609669487161</v>
+        <v>405.86096694871611</v>
       </c>
       <c r="G40">
-        <v>409.1451402091288</v>
+        <v>409.14514020912878</v>
       </c>
       <c r="H40">
-        <v>403.6161640714877</v>
+        <v>403.61616407148767</v>
       </c>
       <c r="I40">
-        <v>406.7929243514413</v>
+        <v>406.79292435144129</v>
       </c>
       <c r="J40">
         <v>423.8772110354584</v>
       </c>
       <c r="K40">
-        <v>403.6074896153258</v>
+        <v>403.60748961532579</v>
       </c>
       <c r="L40">
-        <v>397.5191777022291</v>
+        <v>397.51917770222911</v>
       </c>
       <c r="M40">
-        <v>388.2399891159724</v>
+        <v>388.23998911597238</v>
       </c>
       <c r="N40">
         <v>397.5604471078608</v>
       </c>
       <c r="O40">
-        <v>403.9472725242242</v>
+        <v>403.94727252422422</v>
       </c>
       <c r="P40">
-        <v>411.5357965225782</v>
+        <v>411.53579652257821</v>
       </c>
       <c r="Q40">
-        <v>440.7385249897317</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>440.73852498973167</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>56</v>
       </c>
       <c r="B41">
-        <v>450.6836975203088</v>
+        <v>450.68369752030878</v>
       </c>
       <c r="C41">
         <v>482.9409627904414</v>
       </c>
       <c r="D41">
-        <v>447.3877898761868</v>
+        <v>447.38778987618679</v>
       </c>
       <c r="E41">
-        <v>415.535815794664</v>
+        <v>415.53581579466402</v>
       </c>
       <c r="F41">
         <v>418.7920986241628</v>
       </c>
       <c r="G41">
-        <v>441.5764836439096</v>
+        <v>441.57648364390963</v>
       </c>
       <c r="H41">
-        <v>475.4812287698272</v>
+        <v>475.48122876982723</v>
       </c>
       <c r="I41">
-        <v>470.5133902195522</v>
+        <v>470.51339021955221</v>
       </c>
       <c r="J41">
-        <v>477.9219555777514</v>
+        <v>477.92195557775142</v>
       </c>
       <c r="K41">
         <v>488.1070671994537</v>
       </c>
       <c r="L41">
-        <v>489.5231678013791</v>
+        <v>489.52316780137909</v>
       </c>
       <c r="M41">
-        <v>500.8540357525167</v>
+        <v>500.85403575251672</v>
       </c>
       <c r="N41">
-        <v>499.9044367514036</v>
+        <v>499.90443675140358</v>
       </c>
       <c r="O41">
         <v>508.5716189256774</v>
       </c>
       <c r="P41">
-        <v>518.5772161846787</v>
+        <v>518.57721618467872</v>
       </c>
       <c r="Q41">
-        <v>524.2700099080294</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-        </is>
+        <v>524.27000990802935</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>57</v>
       </c>
       <c r="B42">
-        <v>435.8083355198702</v>
+        <v>435.80833551987018</v>
       </c>
       <c r="C42">
-        <v>482.2132124507592</v>
+        <v>482.21321245075922</v>
       </c>
       <c r="D42">
-        <v>439.7790621402556</v>
+        <v>439.77906214025558</v>
       </c>
       <c r="E42">
-        <v>408.4258245438348</v>
+        <v>408.42582454383478</v>
       </c>
       <c r="F42">
         <v>410.6695851814714</v>
       </c>
       <c r="G42">
-        <v>435.2301778029432</v>
+        <v>435.23017780294322</v>
       </c>
       <c r="H42">
-        <v>462.0208542805941</v>
+        <v>462.02085428059411</v>
       </c>
       <c r="I42">
         <v>446.2981560628578</v>
       </c>
       <c r="J42">
-        <v>449.4372325673488</v>
+        <v>449.43723256734881</v>
       </c>
       <c r="K42">
-        <v>448.1178963588856</v>
+        <v>448.11789635888562</v>
       </c>
       <c r="L42">
-        <v>434.7375961965199</v>
+        <v>434.73759619651992</v>
       </c>
       <c r="M42">
-        <v>435.3658001602414</v>
+        <v>435.36580016024141</v>
       </c>
       <c r="N42">
-        <v>440.6699358129648</v>
+        <v>440.66993581296481</v>
       </c>
       <c r="O42">
-        <v>442.9698869279164</v>
+        <v>442.96988692791638</v>
       </c>
       <c r="P42">
-        <v>454.0279360185893</v>
+        <v>454.02793601858929</v>
       </c>
       <c r="Q42">
-        <v>474.2899597092975</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>474.28995970929748</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>58</v>
       </c>
       <c r="B43">
-        <v>442.3265970225057</v>
+        <v>442.32659702250572</v>
       </c>
       <c r="C43">
         <v>481.0167312783513</v>
       </c>
       <c r="D43">
-        <v>441.2482630751026</v>
+        <v>441.24826307510261</v>
       </c>
       <c r="E43">
-        <v>408.8245043923019</v>
+        <v>408.82450439230189</v>
       </c>
       <c r="F43">
-        <v>412.2218226878978</v>
+        <v>412.22182268789783</v>
       </c>
       <c r="G43">
         <v>433.6785518582393</v>
       </c>
       <c r="H43">
-        <v>460.407022806739</v>
+        <v>460.40702280673901</v>
       </c>
       <c r="I43">
-        <v>441.07109911682</v>
+        <v>441.07109911681999</v>
       </c>
       <c r="J43">
-        <v>443.4989561462916</v>
+        <v>443.49895614629162</v>
       </c>
       <c r="K43">
-        <v>446.4121460383553</v>
+        <v>446.41214603835527</v>
       </c>
       <c r="L43">
         <v>441.6193332940976</v>
       </c>
       <c r="M43">
-        <v>440.7050625265258</v>
+        <v>440.70506252652581</v>
       </c>
       <c r="N43">
-        <v>444.0718082168506</v>
+        <v>444.07180821685063</v>
       </c>
       <c r="O43">
-        <v>442.819165921319</v>
+        <v>442.81916592131898</v>
       </c>
       <c r="P43">
-        <v>446.9300345480908</v>
+        <v>446.93003454809082</v>
       </c>
       <c r="Q43">
-        <v>461.4639743821344</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
+        <v>461.46397438213438</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>59</v>
       </c>
       <c r="B44">
-        <v>507.2580703249463</v>
+        <v>507.25807032494629</v>
       </c>
       <c r="C44">
-        <v>505.7962415786928</v>
+        <v>505.79624157869279</v>
       </c>
       <c r="D44">
-        <v>508.6015703297124</v>
+        <v>508.60157032971239</v>
       </c>
       <c r="E44">
-        <v>486.9102451605596</v>
+        <v>486.91024516055961</v>
       </c>
       <c r="F44">
-        <v>451.522967681298</v>
+        <v>451.52296768129798</v>
       </c>
       <c r="G44">
-        <v>451.0531440123711</v>
+        <v>451.05314401237109</v>
       </c>
       <c r="H44">
-        <v>450.3654820723044</v>
+        <v>450.36548207230442</v>
       </c>
       <c r="I44">
-        <v>464.992633754894</v>
+        <v>464.99263375489397</v>
       </c>
       <c r="J44">
-        <v>467.6365298396869</v>
+        <v>467.63652983968689</v>
       </c>
       <c r="K44">
-        <v>473.9096141301843</v>
+        <v>473.90961413018431</v>
       </c>
       <c r="L44">
-        <v>491.3499037959385</v>
+        <v>491.34990379593847</v>
       </c>
       <c r="M44">
-        <v>514.4014404618478</v>
+        <v>514.40144046184776</v>
       </c>
       <c r="N44">
-        <v>534.7134466761715</v>
+        <v>534.71344667617154</v>
       </c>
       <c r="O44">
-        <v>552.050669096951</v>
+        <v>552.05066909695097</v>
       </c>
       <c r="P44">
-        <v>569.4076179767355</v>
+        <v>569.40761797673554</v>
       </c>
       <c r="Q44">
         <v>592.3280591390436</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>60</v>
       </c>
       <c r="B45">
-        <v>513.3839043302376</v>
+        <v>513.38390433023756</v>
       </c>
       <c r="C45">
-        <v>513.1074501919854</v>
+        <v>513.10745019198544</v>
       </c>
       <c r="D45">
-        <v>490.0343797656819</v>
+        <v>490.03437976568188</v>
       </c>
       <c r="E45">
-        <v>501.0183929139301</v>
+        <v>501.01839291393009</v>
       </c>
       <c r="F45">
-        <v>518.2314361095378</v>
+        <v>518.23143610953775</v>
       </c>
       <c r="G45">
-        <v>544.4069387294329</v>
+        <v>544.40693872943291</v>
       </c>
       <c r="H45">
-        <v>556.8839691992447</v>
+        <v>556.88396919924469</v>
       </c>
       <c r="I45">
         <v>551.7238199889382</v>
       </c>
       <c r="J45">
-        <v>545.908939776535</v>
+        <v>545.90893977653502</v>
       </c>
       <c r="K45">
-        <v>550.9156012428325</v>
+        <v>550.91560124283251</v>
       </c>
       <c r="L45">
-        <v>583.4962274525716</v>
+        <v>583.49622745257159</v>
       </c>
       <c r="M45">
-        <v>610.4770409217734</v>
+        <v>610.47704092177344</v>
       </c>
       <c r="N45">
-        <v>623.0574314156228</v>
+        <v>623.05743141562277</v>
       </c>
       <c r="O45">
-        <v>640.0055580282706</v>
+        <v>640.00555802827057</v>
       </c>
       <c r="P45">
-        <v>648.740798187745</v>
+        <v>648.74079818774499</v>
       </c>
       <c r="Q45">
-        <v>639.7120373493066</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>639.71203734930657</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>61</v>
       </c>
       <c r="B46">
-        <v>507.0030889258966</v>
+        <v>507.00308892589658</v>
       </c>
       <c r="C46">
-        <v>565.5631739623259</v>
+        <v>565.56317396232589</v>
       </c>
       <c r="D46">
-        <v>501.5845374399261</v>
+        <v>501.58453743992612</v>
       </c>
       <c r="E46">
-        <v>507.9217877330151</v>
+        <v>507.92178773301509</v>
       </c>
       <c r="F46">
-        <v>506.1702834921408</v>
+        <v>506.17028349214081</v>
       </c>
       <c r="G46">
-        <v>532.2073988461769</v>
+        <v>532.20739884617694</v>
       </c>
       <c r="H46">
-        <v>524.9015911552506</v>
+        <v>524.90159115525057</v>
       </c>
       <c r="I46">
         <v>523.3621367991459</v>
       </c>
       <c r="J46">
-        <v>551.4166476053194</v>
+        <v>551.41664760531944</v>
       </c>
       <c r="K46">
-        <v>585.3160519469341</v>
+        <v>585.31605194693407</v>
       </c>
       <c r="L46">
-        <v>619.4628092475685</v>
+        <v>619.46280924756854</v>
       </c>
       <c r="M46">
-        <v>626.8651136833427</v>
+        <v>626.86511368334266</v>
       </c>
       <c r="N46">
-        <v>628.6413372492896</v>
+        <v>628.64133724928956</v>
       </c>
       <c r="O46">
-        <v>639.7034422760404</v>
+        <v>639.70344227604039</v>
       </c>
       <c r="P46">
         <v>645.3309333520798</v>
       </c>
       <c r="Q46">
-        <v>645.0506532352765</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
+        <v>645.05065323527651</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>62</v>
       </c>
       <c r="B47">
-        <v>504.3579322247633</v>
+        <v>504.35793222476332</v>
       </c>
       <c r="C47">
-        <v>498.5186318935868</v>
+        <v>498.51863189358681</v>
       </c>
       <c r="D47">
-        <v>503.8178625875403</v>
+        <v>503.81786258754028</v>
       </c>
       <c r="E47">
-        <v>508.6316340969024</v>
+        <v>508.63163409690242</v>
       </c>
       <c r="F47">
-        <v>518.3051220757438</v>
+        <v>518.30512207574384</v>
       </c>
       <c r="G47">
         <v>557.4031818631596</v>
       </c>
       <c r="H47">
-        <v>546.9984361034429</v>
+        <v>546.99843610344294</v>
       </c>
       <c r="I47">
-        <v>536.0488702542817</v>
+        <v>536.04887025428172</v>
       </c>
       <c r="J47">
-        <v>522.0398910900658</v>
+        <v>522.03989109006579</v>
       </c>
       <c r="K47">
-        <v>549.8374300989614</v>
+        <v>549.83743009896136</v>
       </c>
       <c r="L47">
-        <v>548.2177672843438</v>
+        <v>548.21776728434384</v>
       </c>
       <c r="M47">
-        <v>566.9055500111022</v>
+        <v>566.90555001110215</v>
       </c>
       <c r="N47">
-        <v>571.9038951759554</v>
+        <v>571.90389517595543</v>
       </c>
       <c r="O47">
         <v>568.9155471660298</v>
       </c>
       <c r="P47">
-        <v>569.7373913842123</v>
+        <v>569.73739138421229</v>
       </c>
       <c r="Q47">
-        <v>568.1427259099639</v>
+        <v>568.14272590996393</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C2:Q47">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="top10" dxfId="0" priority="1" bottom="1" rank="10"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.carotenes/Resultats_total.carotenes_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.carotenes/Resultats_total.carotenes_moy_RMSEP.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>Pretraitement</t>
   </si>
@@ -27,6 +27,9 @@
     <t>RMSEP_glo</t>
   </si>
   <si>
+    <t>LV0_RMSEP</t>
+  </si>
+  <si>
     <t>LV1_RMSEP</t>
   </si>
   <si>
@@ -136,18 +139,6 @@
   </si>
   <si>
     <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
   </si>
   <si>
     <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
@@ -260,26 +251,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -579,14 +551,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -638,2448 +611,2365 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2">
-        <v>495.1161531195043</v>
+        <v>498.69371264782438</v>
       </c>
       <c r="C2">
-        <v>603.65192217736546</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D2">
-        <v>517.13553430705031</v>
+        <v>602.49641308786147</v>
       </c>
       <c r="E2">
-        <v>496.07608202255602</v>
+        <v>515.76417017192659</v>
       </c>
       <c r="F2">
-        <v>472.19990942334618</v>
+        <v>495.22485263646172</v>
       </c>
       <c r="G2">
-        <v>464.07946049748671</v>
+        <v>472.35688508998658</v>
       </c>
       <c r="H2">
-        <v>450.9424700505171</v>
+        <v>466.32543892499928</v>
       </c>
       <c r="I2">
-        <v>446.36824435532128</v>
+        <v>450.95628537082678</v>
       </c>
       <c r="J2">
-        <v>452.85064485994093</v>
+        <v>445.18004353327069</v>
       </c>
       <c r="K2">
-        <v>461.64972789936269</v>
+        <v>450.22049355558539</v>
       </c>
       <c r="L2">
-        <v>472.81185888299041</v>
+        <v>461.56335701154882</v>
       </c>
       <c r="M2">
-        <v>475.28395442654562</v>
+        <v>472.50427903895638</v>
       </c>
       <c r="N2">
-        <v>496.7770560613701</v>
+        <v>476.83796605614549</v>
       </c>
       <c r="O2">
-        <v>516.31986833724227</v>
+        <v>500.05020209346719</v>
       </c>
       <c r="P2">
-        <v>523.97503925504168</v>
+        <v>517.36655839595062</v>
       </c>
       <c r="Q2">
-        <v>511.85121018523682</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <v>522.24318069181948</v>
+      </c>
+      <c r="R2">
+        <v>511.34291854625428</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3">
-        <v>523.19714897258064</v>
+        <v>520.88738261835431</v>
       </c>
       <c r="C3">
-        <v>564.89028607393527</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D3">
-        <v>508.35561042251658</v>
+        <v>563.90072981635046</v>
       </c>
       <c r="E3">
-        <v>506.82861596492438</v>
+        <v>507.06016867462768</v>
       </c>
       <c r="F3">
-        <v>503.09619852918172</v>
+        <v>504.41084098235609</v>
       </c>
       <c r="G3">
-        <v>510.75343650848879</v>
+        <v>502.24882058189002</v>
       </c>
       <c r="H3">
-        <v>513.13105628149208</v>
+        <v>508.30609126850652</v>
       </c>
       <c r="I3">
-        <v>536.9876094776015</v>
+        <v>510.6739176298957</v>
       </c>
       <c r="J3">
-        <v>543.03313639143357</v>
+        <v>533.82267961533046</v>
       </c>
       <c r="K3">
-        <v>551.04869392753358</v>
+        <v>541.67404307127708</v>
       </c>
       <c r="L3">
-        <v>547.71945998940441</v>
+        <v>550.95108497066917</v>
       </c>
       <c r="M3">
-        <v>558.3171705354539</v>
+        <v>550.74417209289572</v>
       </c>
       <c r="N3">
-        <v>587.1935736747198</v>
+        <v>563.02906038352398</v>
       </c>
       <c r="O3">
-        <v>616.94770811944193</v>
+        <v>592.94775518346557</v>
       </c>
       <c r="P3">
-        <v>637.06996380650173</v>
+        <v>623.80148286959513</v>
       </c>
       <c r="Q3">
-        <v>656.42290296801571</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+        <v>645.73788900526324</v>
+      </c>
+      <c r="R3">
+        <v>664.86806697688849</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4">
-        <v>535.89951061324575</v>
+        <v>529.88260890036634</v>
       </c>
       <c r="C4">
-        <v>593.34150029646776</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D4">
-        <v>525.46333935862515</v>
+        <v>591.67301084985309</v>
       </c>
       <c r="E4">
-        <v>517.40298259820975</v>
+        <v>523.1671374341156</v>
       </c>
       <c r="F4">
-        <v>516.87578550103763</v>
+        <v>513.75197805802088</v>
       </c>
       <c r="G4">
-        <v>508.66113184270267</v>
+        <v>513.98606193941077</v>
       </c>
       <c r="H4">
-        <v>491.05720532531672</v>
+        <v>505.87655930914849</v>
       </c>
       <c r="I4">
-        <v>475.75500391567448</v>
+        <v>488.07949918566322</v>
       </c>
       <c r="J4">
-        <v>490.97613119150589</v>
+        <v>472.63019068982209</v>
       </c>
       <c r="K4">
-        <v>500.34313532868248</v>
+        <v>487.63623620662059</v>
       </c>
       <c r="L4">
-        <v>533.42749325941577</v>
+        <v>496.45736697161288</v>
       </c>
       <c r="M4">
-        <v>543.87716702791533</v>
+        <v>531.53040264822073</v>
       </c>
       <c r="N4">
-        <v>534.58508011833067</v>
+        <v>541.11185150496976</v>
       </c>
       <c r="O4">
-        <v>532.4435001145082</v>
+        <v>530.39188305124799</v>
       </c>
       <c r="P4">
-        <v>536.50905850473771</v>
+        <v>529.96293980204769</v>
       </c>
       <c r="Q4">
-        <v>534.74237755607896</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <v>534.14678578799487</v>
+      </c>
+      <c r="R4">
+        <v>533.75543319607812</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5">
-        <v>517.40006618096845</v>
+        <v>513.81200086326487</v>
       </c>
       <c r="C5">
-        <v>512.94712557763239</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D5">
-        <v>511.47473412768011</v>
+        <v>512.18459415932443</v>
       </c>
       <c r="E5">
-        <v>510.18603072975628</v>
+        <v>510.1327589137735</v>
       </c>
       <c r="F5">
-        <v>515.36867192889918</v>
+        <v>510.53124336687591</v>
       </c>
       <c r="G5">
-        <v>517.63108715683518</v>
+        <v>514.80668082884665</v>
       </c>
       <c r="H5">
-        <v>515.69745011486714</v>
+        <v>517.58152576095188</v>
       </c>
       <c r="I5">
-        <v>518.00417070405103</v>
+        <v>515.93789936888993</v>
       </c>
       <c r="J5">
-        <v>523.49425977903547</v>
+        <v>521.74960086472174</v>
       </c>
       <c r="K5">
-        <v>535.42764712932217</v>
+        <v>528.58991865757685</v>
       </c>
       <c r="L5">
-        <v>539.21811207251267</v>
+        <v>541.61747989862408</v>
       </c>
       <c r="M5">
-        <v>543.75485947428831</v>
+        <v>548.54092693126029</v>
       </c>
       <c r="N5">
-        <v>550.24546938195431</v>
+        <v>553.45495051893886</v>
       </c>
       <c r="O5">
-        <v>551.65526892205844</v>
+        <v>560.7650122413279</v>
       </c>
       <c r="P5">
-        <v>559.26503853732459</v>
+        <v>562.19475985305462</v>
       </c>
       <c r="Q5">
-        <v>552.62368005208054</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>569.09443970285679</v>
+      </c>
+      <c r="R5">
+        <v>560.41324432220438</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6">
-        <v>517.25802836353671</v>
+        <v>515.81207017829877</v>
       </c>
       <c r="C6">
-        <v>512.19963689578742</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D6">
-        <v>508.68300269442062</v>
+        <v>513.48243061575192</v>
       </c>
       <c r="E6">
-        <v>506.42731669375218</v>
+        <v>509.31688262152301</v>
       </c>
       <c r="F6">
-        <v>515.54851371746929</v>
+        <v>506.39503255542797</v>
       </c>
       <c r="G6">
-        <v>503.69584672049251</v>
+        <v>514.8147726509693</v>
       </c>
       <c r="H6">
-        <v>521.46401301042374</v>
+        <v>504.22178178341858</v>
       </c>
       <c r="I6">
-        <v>518.04432995175455</v>
+        <v>521.66678553152747</v>
       </c>
       <c r="J6">
-        <v>530.63794434189924</v>
+        <v>517.73654392812762</v>
       </c>
       <c r="K6">
-        <v>533.00503636156839</v>
+        <v>531.29356354954427</v>
       </c>
       <c r="L6">
-        <v>539.54898636399196</v>
+        <v>532.82988984450003</v>
       </c>
       <c r="M6">
-        <v>556.41456655632794</v>
+        <v>540.00888130649025</v>
       </c>
       <c r="N6">
-        <v>573.5331247139967</v>
+        <v>557.73597230844257</v>
       </c>
       <c r="O6">
-        <v>586.04305913512349</v>
+        <v>571.58294900229805</v>
       </c>
       <c r="P6">
-        <v>586.63237137586418</v>
+        <v>586.01220271101124</v>
       </c>
       <c r="Q6">
-        <v>570.33500552601117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <v>584.95518660469713</v>
+      </c>
+      <c r="R6">
+        <v>567.865365525519</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7">
-        <v>462.92513060634428</v>
+        <v>459.51510748161002</v>
       </c>
       <c r="C7">
-        <v>594.49402265099866</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D7">
-        <v>517.7359404524791</v>
+        <v>592.43902375791254</v>
       </c>
       <c r="E7">
-        <v>472.87884302486049</v>
+        <v>513.79287275510842</v>
       </c>
       <c r="F7">
-        <v>447.22430932797391</v>
+        <v>470.57015833275079</v>
       </c>
       <c r="G7">
-        <v>434.06691574940788</v>
+        <v>446.01176354183832</v>
       </c>
       <c r="H7">
-        <v>425.74112234617928</v>
+        <v>433.95666220178532</v>
       </c>
       <c r="I7">
-        <v>436.56717341059601</v>
+        <v>423.67481969710468</v>
       </c>
       <c r="J7">
-        <v>443.71986322078959</v>
+        <v>436.80217683386348</v>
       </c>
       <c r="K7">
-        <v>453.17532260193269</v>
+        <v>443.87237220823971</v>
       </c>
       <c r="L7">
-        <v>452.32126557547502</v>
+        <v>452.88368650762288</v>
       </c>
       <c r="M7">
-        <v>486.9977907423476</v>
+        <v>453.23821408035792</v>
       </c>
       <c r="N7">
-        <v>486.27013932084992</v>
+        <v>487.8326820319931</v>
       </c>
       <c r="O7">
-        <v>477.68972198377998</v>
+        <v>488.14447179286088</v>
       </c>
       <c r="P7">
-        <v>478.67120651262587</v>
+        <v>478.5337721646585</v>
       </c>
       <c r="Q7">
-        <v>478.89099813315988</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <v>480.37300258906038</v>
+      </c>
+      <c r="R7">
+        <v>481.23995256430499</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8">
-        <v>526.60063098434239</v>
+        <v>529.70087198193346</v>
       </c>
       <c r="C8">
-        <v>565.20346184836774</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D8">
-        <v>528.36346762032031</v>
+        <v>565.19537188746494</v>
       </c>
       <c r="E8">
-        <v>499.23868411865868</v>
+        <v>526.91912634259256</v>
       </c>
       <c r="F8">
-        <v>487.12280520526781</v>
+        <v>497.16209967344389</v>
       </c>
       <c r="G8">
-        <v>485.01035616636273</v>
+        <v>485.70338011922269</v>
       </c>
       <c r="H8">
-        <v>487.81361438195239</v>
+        <v>483.49400214740928</v>
       </c>
       <c r="I8">
-        <v>480.1520510162365</v>
+        <v>484.36377677903653</v>
       </c>
       <c r="J8">
-        <v>475.58048148367908</v>
+        <v>477.5658265967358</v>
       </c>
       <c r="K8">
-        <v>509.5834611422278</v>
+        <v>472.92158666869813</v>
       </c>
       <c r="L8">
-        <v>529.11452214647693</v>
+        <v>505.96861872830323</v>
       </c>
       <c r="M8">
-        <v>531.07438421222503</v>
+        <v>525.85956549845741</v>
       </c>
       <c r="N8">
-        <v>524.60466878016632</v>
+        <v>528.26040975984495</v>
       </c>
       <c r="O8">
-        <v>510.74049044317718</v>
+        <v>520.9352116045568</v>
       </c>
       <c r="P8">
-        <v>521.66651300385854</v>
+        <v>508.58439814935349</v>
       </c>
       <c r="Q8">
-        <v>519.36326787508619</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <v>520.98151095248022</v>
+      </c>
+      <c r="R8">
+        <v>518.55000813327194</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9">
-        <v>530.09207956643354</v>
+        <v>534.48112671143076</v>
       </c>
       <c r="C9">
-        <v>564.31797323283422</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D9">
-        <v>527.67358990012201</v>
+        <v>564.63300766903842</v>
       </c>
       <c r="E9">
-        <v>501.60799822898031</v>
+        <v>528.19190517600009</v>
       </c>
       <c r="F9">
-        <v>491.41973994602148</v>
+        <v>500.84337412336168</v>
       </c>
       <c r="G9">
-        <v>487.35162391940531</v>
+        <v>489.53395569179622</v>
       </c>
       <c r="H9">
-        <v>489.37543780356009</v>
+        <v>486.56985784408357</v>
       </c>
       <c r="I9">
-        <v>484.3937459231629</v>
+        <v>488.86410621979121</v>
       </c>
       <c r="J9">
-        <v>478.64603718944761</v>
+        <v>481.96876560067471</v>
       </c>
       <c r="K9">
-        <v>500.02826977884553</v>
+        <v>475.90496776425431</v>
       </c>
       <c r="L9">
-        <v>519.82558582240745</v>
+        <v>496.71525183121622</v>
       </c>
       <c r="M9">
-        <v>530.08897548632513</v>
+        <v>512.09936208287786</v>
       </c>
       <c r="N9">
-        <v>522.1018022086962</v>
+        <v>521.20977293349733</v>
       </c>
       <c r="O9">
-        <v>505.99814331977501</v>
+        <v>512.70699950749167</v>
       </c>
       <c r="P9">
-        <v>515.94658819652943</v>
+        <v>497.55897130309557</v>
       </c>
       <c r="Q9">
-        <v>517.10482120703205</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>506.20067864625099</v>
+      </c>
+      <c r="R9">
+        <v>510.38633776100068</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10">
-        <v>539.65020124462342</v>
+        <v>531.69710221363266</v>
       </c>
       <c r="C10">
-        <v>565.06954144637359</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D10">
-        <v>527.72476965376211</v>
+        <v>564.5842280936879</v>
       </c>
       <c r="E10">
-        <v>501.49439662089469</v>
+        <v>527.74728802869595</v>
       </c>
       <c r="F10">
-        <v>490.08963334677242</v>
+        <v>500.02536058803048</v>
       </c>
       <c r="G10">
-        <v>489.33853287206512</v>
+        <v>489.71759484365668</v>
       </c>
       <c r="H10">
-        <v>490.05706753918793</v>
+        <v>488.58061754171752</v>
       </c>
       <c r="I10">
-        <v>485.21530214089017</v>
+        <v>490.04252085090269</v>
       </c>
       <c r="J10">
-        <v>478.4077706099738</v>
+        <v>485.34086712387239</v>
       </c>
       <c r="K10">
-        <v>500.33434109376759</v>
+        <v>478.65374056968949</v>
       </c>
       <c r="L10">
-        <v>516.27454183517227</v>
+        <v>499.06803555606569</v>
       </c>
       <c r="M10">
-        <v>527.42136895728424</v>
+        <v>515.945313050001</v>
       </c>
       <c r="N10">
-        <v>519.66581712094671</v>
+        <v>526.9428342107683</v>
       </c>
       <c r="O10">
-        <v>502.79077022766552</v>
+        <v>518.89197475312869</v>
       </c>
       <c r="P10">
-        <v>506.19465039879339</v>
+        <v>501.34761954605449</v>
       </c>
       <c r="Q10">
-        <v>509.67167515012432</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <v>505.46130382702722</v>
+      </c>
+      <c r="R10">
+        <v>507.61068330358512</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11">
-        <v>536.24520027797587</v>
+        <v>536.00433280036043</v>
       </c>
       <c r="C11">
-        <v>564.66752069162374</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D11">
-        <v>528.31796691511363</v>
+        <v>566.70634150530111</v>
       </c>
       <c r="E11">
-        <v>500.67032296420177</v>
+        <v>530.12869513393093</v>
       </c>
       <c r="F11">
-        <v>490.36429709296681</v>
+        <v>503.45956057751113</v>
       </c>
       <c r="G11">
-        <v>487.3979436442221</v>
+        <v>492.83902984103531</v>
       </c>
       <c r="H11">
-        <v>491.67747381752241</v>
+        <v>489.01413358146158</v>
       </c>
       <c r="I11">
-        <v>485.380501234615</v>
+        <v>495.33360997763452</v>
       </c>
       <c r="J11">
-        <v>477.58899372848072</v>
+        <v>487.88141640627322</v>
       </c>
       <c r="K11">
-        <v>499.19117769688648</v>
+        <v>482.23362871005679</v>
       </c>
       <c r="L11">
-        <v>515.88137485132188</v>
+        <v>503.54345674017873</v>
       </c>
       <c r="M11">
-        <v>524.42893393125075</v>
+        <v>519.7307284936395</v>
       </c>
       <c r="N11">
-        <v>516.71841139288108</v>
+        <v>531.43406022909733</v>
       </c>
       <c r="O11">
-        <v>505.38933037508451</v>
+        <v>522.28954177820276</v>
       </c>
       <c r="P11">
-        <v>514.39961577063855</v>
+        <v>509.25917241183078</v>
       </c>
       <c r="Q11">
-        <v>506.99690978710379</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>518.94158601335107</v>
+      </c>
+      <c r="R11">
+        <v>511.37407383313069</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12">
-        <v>510.0812827762598</v>
+        <v>512.97481457924368</v>
       </c>
       <c r="C12">
-        <v>505.9985358331819</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D12">
-        <v>501.3742840778537</v>
+        <v>507.44407457959011</v>
       </c>
       <c r="E12">
-        <v>498.41540565887209</v>
+        <v>504.15285356908493</v>
       </c>
       <c r="F12">
-        <v>496.37864824305723</v>
+        <v>500.87979702945279</v>
       </c>
       <c r="G12">
-        <v>490.7961644302739</v>
+        <v>498.02558678847828</v>
       </c>
       <c r="H12">
-        <v>488.50127820140187</v>
+        <v>491.86270587117713</v>
       </c>
       <c r="I12">
-        <v>489.10688180979838</v>
+        <v>490.59275773014701</v>
       </c>
       <c r="J12">
-        <v>495.37380974637688</v>
+        <v>492.20281653819399</v>
       </c>
       <c r="K12">
-        <v>503.02723406307058</v>
+        <v>498.79344200602242</v>
       </c>
       <c r="L12">
-        <v>514.03482597420054</v>
+        <v>509.19623253466852</v>
       </c>
       <c r="M12">
-        <v>529.65968405130991</v>
+        <v>518.91895115644957</v>
       </c>
       <c r="N12">
-        <v>544.04302849986175</v>
+        <v>535.33333377569147</v>
       </c>
       <c r="O12">
-        <v>549.57035862041243</v>
+        <v>550.86335882576725</v>
       </c>
       <c r="P12">
-        <v>557.83172902151944</v>
+        <v>553.8410477232585</v>
       </c>
       <c r="Q12">
-        <v>563.30331282890995</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <v>561.60291774360053</v>
+      </c>
+      <c r="R12">
+        <v>567.19745308527285</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13">
-        <v>509.98422727818149</v>
+        <v>513.09205887058283</v>
       </c>
       <c r="C13">
-        <v>507.485223692305</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D13">
-        <v>495.95186756434299</v>
+        <v>508.24802772920663</v>
       </c>
       <c r="E13">
-        <v>488.07653953463517</v>
+        <v>497.75325589192971</v>
       </c>
       <c r="F13">
-        <v>485.38967296918918</v>
+        <v>492.45332396991472</v>
       </c>
       <c r="G13">
-        <v>490.56804216038978</v>
+        <v>490.92096355929419</v>
       </c>
       <c r="H13">
-        <v>494.10872770652969</v>
+        <v>495.82140844936032</v>
       </c>
       <c r="I13">
-        <v>495.38620479464657</v>
+        <v>500.82276808546698</v>
       </c>
       <c r="J13">
-        <v>505.62191605351592</v>
+        <v>501.22026463778798</v>
       </c>
       <c r="K13">
-        <v>512.10124408459251</v>
+        <v>512.71649083484283</v>
       </c>
       <c r="L13">
-        <v>528.06316784432408</v>
+        <v>521.63510141230779</v>
       </c>
       <c r="M13">
-        <v>534.37196025680055</v>
+        <v>538.79681196907859</v>
       </c>
       <c r="N13">
-        <v>538.71538458264047</v>
+        <v>545.14998489762866</v>
       </c>
       <c r="O13">
-        <v>544.05647457144676</v>
+        <v>550.35876335159435</v>
       </c>
       <c r="P13">
-        <v>552.55470908788254</v>
+        <v>559.14967103484753</v>
       </c>
       <c r="Q13">
-        <v>567.97363742366986</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <v>565.32220212276343</v>
+      </c>
+      <c r="R13">
+        <v>580.90307438071375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14">
-        <v>463.0950551255109</v>
+        <v>462.0394164811168</v>
       </c>
       <c r="C14">
-        <v>593.30329271282039</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D14">
-        <v>516.398945182273</v>
+        <v>591.88915676168244</v>
       </c>
       <c r="E14">
-        <v>472.7668528910869</v>
+        <v>514.86263691275394</v>
       </c>
       <c r="F14">
-        <v>447.00928537878298</v>
+        <v>470.76081151920943</v>
       </c>
       <c r="G14">
-        <v>435.2613696765182</v>
+        <v>445.14202582692639</v>
       </c>
       <c r="H14">
-        <v>427.74712669274891</v>
+        <v>433.77526883806769</v>
       </c>
       <c r="I14">
-        <v>437.24471946742079</v>
+        <v>427.07543989209103</v>
       </c>
       <c r="J14">
-        <v>442.90420143327219</v>
+        <v>435.8677515112185</v>
       </c>
       <c r="K14">
-        <v>450.84436658833971</v>
+        <v>444.40112262785073</v>
       </c>
       <c r="L14">
-        <v>451.1290291878538</v>
+        <v>450.76440025302838</v>
       </c>
       <c r="M14">
-        <v>487.34073967558191</v>
+        <v>452.70593711383572</v>
       </c>
       <c r="N14">
-        <v>496.67779955503943</v>
+        <v>488.42510141200052</v>
       </c>
       <c r="O14">
-        <v>490.9468779464604</v>
+        <v>498.11785727527513</v>
       </c>
       <c r="P14">
-        <v>489.27161860008772</v>
+        <v>493.90873874391463</v>
       </c>
       <c r="Q14">
-        <v>479.04992467370539</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+        <v>492.44769482939108</v>
+      </c>
+      <c r="R14">
+        <v>484.35513680642288</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15">
-        <v>463.63984427172772</v>
+        <v>461.30793106037117</v>
       </c>
       <c r="C15">
-        <v>594.12295992431905</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D15">
-        <v>517.58049797529657</v>
+        <v>593.59720262759083</v>
       </c>
       <c r="E15">
-        <v>472.7956289322762</v>
+        <v>516.76671544424914</v>
       </c>
       <c r="F15">
-        <v>446.19993613537662</v>
+        <v>469.82942218482742</v>
       </c>
       <c r="G15">
-        <v>434.76066503327638</v>
+        <v>445.50943274924089</v>
       </c>
       <c r="H15">
-        <v>427.71373421178481</v>
+        <v>433.95475640514928</v>
       </c>
       <c r="I15">
-        <v>436.78298384833971</v>
+        <v>426.42068244986592</v>
       </c>
       <c r="J15">
-        <v>442.99219232972382</v>
+        <v>435.8183520226554</v>
       </c>
       <c r="K15">
-        <v>450.79457429141678</v>
+        <v>441.08070592497762</v>
       </c>
       <c r="L15">
-        <v>451.28041791372812</v>
+        <v>447.69723849941812</v>
       </c>
       <c r="M15">
-        <v>485.69398577425278</v>
+        <v>448.77320743277102</v>
       </c>
       <c r="N15">
-        <v>496.09927387846272</v>
+        <v>482.25870816719367</v>
       </c>
       <c r="O15">
-        <v>493.40129144541407</v>
+        <v>493.56775236581132</v>
       </c>
       <c r="P15">
-        <v>492.65557643680501</v>
+        <v>489.96394535585642</v>
       </c>
       <c r="Q15">
-        <v>482.09024677470921</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+        <v>488.72136834503249</v>
+      </c>
+      <c r="R15">
+        <v>478.33312120243642</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16">
-        <v>462.18868472330291</v>
+        <v>459.9576150612458</v>
       </c>
       <c r="C16">
-        <v>593.10691399436632</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D16">
-        <v>515.5769610059931</v>
+        <v>591.82527011415539</v>
       </c>
       <c r="E16">
-        <v>469.1481206011789</v>
+        <v>514.50277273205165</v>
       </c>
       <c r="F16">
-        <v>445.38623547845771</v>
+        <v>469.47952704159349</v>
       </c>
       <c r="G16">
-        <v>433.20672009397867</v>
+        <v>444.85593199024498</v>
       </c>
       <c r="H16">
-        <v>426.59865128627928</v>
+        <v>432.77530763948698</v>
       </c>
       <c r="I16">
-        <v>435.66899612175848</v>
+        <v>425.23802506676998</v>
       </c>
       <c r="J16">
-        <v>441.47430186287983</v>
+        <v>434.95647049184203</v>
       </c>
       <c r="K16">
-        <v>449.44055003696371</v>
+        <v>439.04281206898929</v>
       </c>
       <c r="L16">
-        <v>450.5182709443813</v>
+        <v>447.82790321307601</v>
       </c>
       <c r="M16">
-        <v>484.17417332303938</v>
+        <v>448.4847009476112</v>
       </c>
       <c r="N16">
-        <v>493.05128346515619</v>
+        <v>480.92609288191682</v>
       </c>
       <c r="O16">
-        <v>491.24032126169033</v>
+        <v>489.79925226952298</v>
       </c>
       <c r="P16">
-        <v>491.54076808292899</v>
+        <v>488.53280362894247</v>
       </c>
       <c r="Q16">
-        <v>483.54221320038653</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <v>487.84288230499601</v>
+      </c>
+      <c r="R16">
+        <v>479.38459249232523</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17">
-        <v>463.9003890237438</v>
+        <v>459.80859204305312</v>
       </c>
       <c r="C17">
-        <v>592.51629142091315</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D17">
-        <v>515.73259702771225</v>
+        <v>592.10869051178986</v>
       </c>
       <c r="E17">
-        <v>471.46662879282729</v>
+        <v>514.53028290262762</v>
       </c>
       <c r="F17">
-        <v>447.17807382846507</v>
+        <v>470.4880273025035</v>
       </c>
       <c r="G17">
-        <v>436.08341984897658</v>
+        <v>445.35107639217438</v>
       </c>
       <c r="H17">
-        <v>427.58921598328811</v>
+        <v>432.68637338989669</v>
       </c>
       <c r="I17">
-        <v>437.13428986909929</v>
+        <v>425.13654956251219</v>
       </c>
       <c r="J17">
-        <v>442.09464075102568</v>
+        <v>434.13113275396842</v>
       </c>
       <c r="K17">
-        <v>450.98612814477173</v>
+        <v>439.51080529786577</v>
       </c>
       <c r="L17">
-        <v>451.23878066539191</v>
+        <v>447.17264720648319</v>
       </c>
       <c r="M17">
-        <v>485.43317047857329</v>
+        <v>447.26788225608271</v>
       </c>
       <c r="N17">
-        <v>494.95785680246058</v>
+        <v>479.95092748905898</v>
       </c>
       <c r="O17">
-        <v>490.31752075595631</v>
+        <v>487.43063837819238</v>
       </c>
       <c r="P17">
-        <v>487.4905088753265</v>
+        <v>483.0081890402131</v>
       </c>
       <c r="Q17">
-        <v>478.43611076406302</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <v>480.17189378553411</v>
+      </c>
+      <c r="R17">
+        <v>471.15116624167592</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18">
-        <v>510.57229507462517</v>
+        <v>511.47609049992229</v>
       </c>
       <c r="C18">
-        <v>505.18345482074278</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D18">
-        <v>501.39252529338319</v>
+        <v>505.18212722386602</v>
       </c>
       <c r="E18">
-        <v>498.50152276328629</v>
+        <v>501.79993663140738</v>
       </c>
       <c r="F18">
-        <v>496.79273254858202</v>
+        <v>499.2147753063519</v>
       </c>
       <c r="G18">
-        <v>483.85169087092282</v>
+        <v>497.8226525233531</v>
       </c>
       <c r="H18">
-        <v>488.56176387368163</v>
+        <v>482.66631201801482</v>
       </c>
       <c r="I18">
-        <v>483.14361147396721</v>
+        <v>489.12159493313118</v>
       </c>
       <c r="J18">
-        <v>488.58459619997438</v>
+        <v>482.22778173756859</v>
       </c>
       <c r="K18">
-        <v>486.52888190941292</v>
+        <v>486.95217757982971</v>
       </c>
       <c r="L18">
-        <v>488.43422766955558</v>
+        <v>487.42473450746428</v>
       </c>
       <c r="M18">
-        <v>489.79109257373051</v>
+        <v>490.5031992169811</v>
       </c>
       <c r="N18">
-        <v>495.66201010356178</v>
+        <v>490.02610187412103</v>
       </c>
       <c r="O18">
-        <v>496.60676868729189</v>
+        <v>497.02072345633479</v>
       </c>
       <c r="P18">
-        <v>507.43950073345559</v>
+        <v>497.70933297738623</v>
       </c>
       <c r="Q18">
-        <v>506.70945460019618</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <v>507.80760073443241</v>
+      </c>
+      <c r="R18">
+        <v>504.55348187452921</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19">
-        <v>509.26379965581958</v>
+        <v>511.05937064089318</v>
       </c>
       <c r="C19">
-        <v>504.65368039151912</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D19">
-        <v>498.62934932937731</v>
+        <v>503.8838349655262</v>
       </c>
       <c r="E19">
-        <v>494.89700661950872</v>
+        <v>498.69448859516058</v>
       </c>
       <c r="F19">
-        <v>499.76839702671788</v>
+        <v>495.04611375270071</v>
       </c>
       <c r="G19">
-        <v>484.26509208717329</v>
+        <v>499.37323097742649</v>
       </c>
       <c r="H19">
-        <v>490.71242971123729</v>
+        <v>483.73110203344447</v>
       </c>
       <c r="I19">
-        <v>485.03450205516111</v>
+        <v>490.71056804786002</v>
       </c>
       <c r="J19">
-        <v>484.37125645516289</v>
+        <v>486.979690413821</v>
       </c>
       <c r="K19">
-        <v>487.0281615471024</v>
+        <v>491.29075967606298</v>
       </c>
       <c r="L19">
-        <v>479.59993887458518</v>
+        <v>492.67927802172079</v>
       </c>
       <c r="M19">
-        <v>494.52943776966418</v>
+        <v>485.21759972746901</v>
       </c>
       <c r="N19">
-        <v>501.95147281512169</v>
+        <v>501.4499989557948</v>
       </c>
       <c r="O19">
-        <v>506.78546374416419</v>
+        <v>507.24011324918962</v>
       </c>
       <c r="P19">
-        <v>508.71002372280321</v>
+        <v>508.20012006702621</v>
       </c>
       <c r="Q19">
-        <v>505.45310187052968</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+        <v>510.55586160445762</v>
+      </c>
+      <c r="R19">
+        <v>505.27443328806032</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20">
-        <v>510.13120902100451</v>
+        <v>509.59028476506978</v>
       </c>
       <c r="C20">
-        <v>503.95395573840131</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D20">
-        <v>497.21841128042928</v>
+        <v>504.38872243902642</v>
       </c>
       <c r="E20">
-        <v>488.60402362744611</v>
+        <v>497.7317527374405</v>
       </c>
       <c r="F20">
-        <v>496.27215024212012</v>
+        <v>488.92944846117831</v>
       </c>
       <c r="G20">
-        <v>490.52487652344689</v>
+        <v>496.47417361990182</v>
       </c>
       <c r="H20">
-        <v>479.87274242170389</v>
+        <v>491.57636660612161</v>
       </c>
       <c r="I20">
-        <v>476.8904152818252</v>
+        <v>479.92958958818792</v>
       </c>
       <c r="J20">
-        <v>477.53319615524481</v>
+        <v>477.813274991924</v>
       </c>
       <c r="K20">
-        <v>478.74169614318947</v>
+        <v>479.89392958177632</v>
       </c>
       <c r="L20">
-        <v>479.90177425917608</v>
+        <v>481.42790171275283</v>
       </c>
       <c r="M20">
-        <v>489.1619874442664</v>
+        <v>482.46037691398527</v>
       </c>
       <c r="N20">
-        <v>502.4036768187168</v>
+        <v>492.0369742628917</v>
       </c>
       <c r="O20">
-        <v>507.90648967752412</v>
+        <v>504.43843668440581</v>
       </c>
       <c r="P20">
-        <v>495.32111643933041</v>
+        <v>506.39483376325558</v>
       </c>
       <c r="Q20">
-        <v>494.97156473566082</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+        <v>490.90736589660048</v>
+      </c>
+      <c r="R20">
+        <v>491.08148433122648</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21">
-        <v>517.70900042713049</v>
+        <v>514.14859514568263</v>
       </c>
       <c r="C21">
-        <v>564.06107335896104</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D21">
-        <v>508.95718392353172</v>
+        <v>563.85034990425811</v>
       </c>
       <c r="E21">
-        <v>505.76105687414707</v>
+        <v>508.21095835532219</v>
       </c>
       <c r="F21">
-        <v>498.87884072696141</v>
+        <v>503.83251374187631</v>
       </c>
       <c r="G21">
-        <v>500.72793508107708</v>
+        <v>496.58029760365741</v>
       </c>
       <c r="H21">
-        <v>508.34749716517138</v>
+        <v>497.27658537206719</v>
       </c>
       <c r="I21">
-        <v>542.55613957933224</v>
+        <v>502.63717520838588</v>
       </c>
       <c r="J21">
-        <v>552.46006930675992</v>
+        <v>534.83247560946302</v>
       </c>
       <c r="K21">
-        <v>552.32927878786018</v>
+        <v>543.62617321494895</v>
       </c>
       <c r="L21">
-        <v>564.322546065496</v>
+        <v>549.185000810102</v>
       </c>
       <c r="M21">
-        <v>577.54810259953433</v>
+        <v>559.21043226209395</v>
       </c>
       <c r="N21">
-        <v>594.91934864801635</v>
+        <v>573.8160114824741</v>
       </c>
       <c r="O21">
-        <v>613.92424171264656</v>
+        <v>591.02486232615331</v>
       </c>
       <c r="P21">
-        <v>637.04029362215272</v>
+        <v>609.60855702942592</v>
       </c>
       <c r="Q21">
-        <v>664.81608403273754</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+        <v>632.5452998339257</v>
+      </c>
+      <c r="R21">
+        <v>659.56962282075676</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22">
-        <v>515.9863874956385</v>
+        <v>515.39837118575235</v>
       </c>
       <c r="C22">
-        <v>565.05412473006834</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D22">
-        <v>509.92324442444323</v>
+        <v>563.86491532829098</v>
       </c>
       <c r="E22">
-        <v>506.03923245988642</v>
+        <v>509.26084408220612</v>
       </c>
       <c r="F22">
-        <v>498.62727994503922</v>
+        <v>506.49054974759889</v>
       </c>
       <c r="G22">
-        <v>497.25321244778519</v>
+        <v>498.44267985401768</v>
       </c>
       <c r="H22">
-        <v>495.68121939524411</v>
+        <v>499.491600866581</v>
       </c>
       <c r="I22">
-        <v>530.05380528497801</v>
+        <v>497.61439127603711</v>
       </c>
       <c r="J22">
-        <v>546.4362217332075</v>
+        <v>532.06713765850657</v>
       </c>
       <c r="K22">
-        <v>544.33040317747486</v>
+        <v>546.78044106882305</v>
       </c>
       <c r="L22">
-        <v>554.16353196232069</v>
+        <v>545.93241134417258</v>
       </c>
       <c r="M22">
-        <v>569.32127558145464</v>
+        <v>553.57798466173517</v>
       </c>
       <c r="N22">
-        <v>587.55183079231131</v>
+        <v>570.51233236057271</v>
       </c>
       <c r="O22">
-        <v>602.930661599725</v>
+        <v>589.33114086157207</v>
       </c>
       <c r="P22">
-        <v>625.12384588824807</v>
+        <v>605.52967342794477</v>
       </c>
       <c r="Q22">
-        <v>647.21758631331784</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+        <v>629.67221653629963</v>
+      </c>
+      <c r="R22">
+        <v>652.91269460558283</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23">
-        <v>507.23680231081448</v>
+        <v>507.72195280722917</v>
       </c>
       <c r="C23">
-        <v>506.98549654072832</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D23">
-        <v>516.73021229184951</v>
+        <v>507.1545024050705</v>
       </c>
       <c r="E23">
-        <v>507.99697488191981</v>
+        <v>518.35032762158858</v>
       </c>
       <c r="F23">
-        <v>500.18663826625681</v>
+        <v>507.48728907914631</v>
       </c>
       <c r="G23">
-        <v>524.05833631939254</v>
+        <v>498.70012100991369</v>
       </c>
       <c r="H23">
-        <v>559.94419339399667</v>
+        <v>522.09981530893026</v>
       </c>
       <c r="I23">
-        <v>590.96712012838611</v>
+        <v>557.24936982669874</v>
       </c>
       <c r="J23">
-        <v>593.63173351664852</v>
+        <v>588.6033753485525</v>
       </c>
       <c r="K23">
-        <v>614.66801396903065</v>
+        <v>591.83592946311774</v>
       </c>
       <c r="L23">
-        <v>626.72359799074877</v>
+        <v>610.91338183906896</v>
       </c>
       <c r="M23">
-        <v>647.10958091758539</v>
+        <v>623.65866831887945</v>
       </c>
       <c r="N23">
-        <v>654.80655523388782</v>
+        <v>644.44360352437616</v>
       </c>
       <c r="O23">
-        <v>675.96550016339893</v>
+        <v>652.35017910401587</v>
       </c>
       <c r="P23">
-        <v>691.90605006882322</v>
+        <v>673.63048716640481</v>
       </c>
       <c r="Q23">
-        <v>713.69298166303145</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+        <v>690.84515974494809</v>
+      </c>
+      <c r="R23">
+        <v>714.30126634442877</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24">
-        <v>716.79819185283566</v>
+        <v>456.51065103350999</v>
       </c>
       <c r="C24">
-        <v>716.79819185283566</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D24">
-        <v>738.51339643760105</v>
+        <v>494.24416943450399</v>
       </c>
       <c r="E24">
-        <v>728.84565491712431</v>
+        <v>457.99164520980509</v>
       </c>
       <c r="F24">
-        <v>763.68361940174782</v>
+        <v>436.72035793525862</v>
       </c>
       <c r="G24">
-        <v>866.72222813315057</v>
+        <v>422.50557941019031</v>
       </c>
       <c r="H24">
-        <v>827.16082328251491</v>
+        <v>435.93978948194098</v>
       </c>
       <c r="I24">
-        <v>847.25905038437247</v>
+        <v>438.07663654726122</v>
       </c>
       <c r="J24">
-        <v>867.0342701071919</v>
+        <v>440.58454223732912</v>
       </c>
       <c r="K24">
-        <v>891.7997214528599</v>
+        <v>450.5051456854888</v>
       </c>
       <c r="L24">
-        <v>905.09711404527093</v>
+        <v>436.76339770996321</v>
       </c>
       <c r="M24">
-        <v>918.73023104237586</v>
+        <v>431.67002024336477</v>
       </c>
       <c r="N24">
-        <v>914.98994458058428</v>
+        <v>442.90628551594568</v>
       </c>
       <c r="O24">
-        <v>913.31161600846735</v>
+        <v>459.80284191582359</v>
       </c>
       <c r="P24">
-        <v>920.10564840432733</v>
+        <v>477.49617527184472</v>
       </c>
       <c r="Q24">
-        <v>925.98701785405137</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+        <v>490.40053123712983</v>
+      </c>
+      <c r="R24">
+        <v>508.99849529959442</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25">
-        <v>726.2555492366796</v>
+        <v>425.8168304557351</v>
       </c>
       <c r="C25">
-        <v>726.2555492366796</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D25">
-        <v>741.70124142614213</v>
+        <v>495.92068784421423</v>
       </c>
       <c r="E25">
-        <v>755.63835669361674</v>
+        <v>457.45608128814717</v>
       </c>
       <c r="F25">
-        <v>786.59512630954464</v>
+        <v>429.32281184592938</v>
       </c>
       <c r="G25">
-        <v>811.1082209835314</v>
+        <v>407.60137171259862</v>
       </c>
       <c r="H25">
-        <v>860.87041336127095</v>
+        <v>411.96028175074019</v>
       </c>
       <c r="I25">
-        <v>899.0400567244476</v>
+        <v>404.24632182196399</v>
       </c>
       <c r="J25">
-        <v>926.5176348352544</v>
+        <v>408.9631719308797</v>
       </c>
       <c r="K25">
-        <v>938.04181303657015</v>
+        <v>418.8190275581469</v>
       </c>
       <c r="L25">
-        <v>942.0056548167704</v>
+        <v>391.75187071834449</v>
       </c>
       <c r="M25">
-        <v>965.48531523722443</v>
+        <v>391.04493057143782</v>
       </c>
       <c r="N25">
-        <v>988.18917673537339</v>
+        <v>390.16579707977343</v>
       </c>
       <c r="O25">
-        <v>1005.5990362779499</v>
+        <v>403.77022459292112</v>
       </c>
       <c r="P25">
-        <v>1013.708178225481</v>
+        <v>413.9344303695774</v>
       </c>
       <c r="Q25">
-        <v>1020.709337425577</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+        <v>428.83724479388951</v>
+      </c>
+      <c r="R25">
+        <v>446.93008903144442</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26">
-        <v>723.60236826425182</v>
+        <v>469.54987147186819</v>
       </c>
       <c r="C26">
-        <v>723.60236826425171</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D26">
-        <v>736.37364441927798</v>
+        <v>484.87799889472689</v>
       </c>
       <c r="E26">
-        <v>734.72606099538257</v>
+        <v>465.50937240197538</v>
       </c>
       <c r="F26">
-        <v>759.99468420251117</v>
+        <v>443.63897517811051</v>
       </c>
       <c r="G26">
-        <v>795.06539850107458</v>
+        <v>422.86298923310301</v>
       </c>
       <c r="H26">
-        <v>802.12878713663019</v>
+        <v>435.65304973857133</v>
       </c>
       <c r="I26">
-        <v>829.02345680651911</v>
+        <v>424.94982572783817</v>
       </c>
       <c r="J26">
-        <v>822.23337809965324</v>
+        <v>423.15682402675509</v>
       </c>
       <c r="K26">
-        <v>801.50610198383356</v>
+        <v>426.33291779961661</v>
       </c>
       <c r="L26">
-        <v>781.80752251935144</v>
+        <v>426.26433823943307</v>
       </c>
       <c r="M26">
-        <v>837.15743314347299</v>
+        <v>417.08670075953569</v>
       </c>
       <c r="N26">
-        <v>884.01584990655033</v>
+        <v>423.12105782143351</v>
       </c>
       <c r="O26">
-        <v>867.97574603305156</v>
+        <v>425.95265945035533</v>
       </c>
       <c r="P26">
-        <v>875.95145207375469</v>
+        <v>440.49648099642769</v>
       </c>
       <c r="Q26">
-        <v>879.07882500140386</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+        <v>457.83150404568562</v>
+      </c>
+      <c r="R26">
+        <v>476.523414304553</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27">
-        <v>731.14751808438461</v>
+        <v>476.02836920298307</v>
       </c>
       <c r="C27">
-        <v>729.66424605370162</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D27">
-        <v>735.67940848706894</v>
+        <v>484.52591911765728</v>
       </c>
       <c r="E27">
-        <v>774.9149750811406</v>
+        <v>465.89510685882851</v>
       </c>
       <c r="F27">
-        <v>755.4041814496843</v>
+        <v>443.05918269525432</v>
       </c>
       <c r="G27">
-        <v>796.78628526712964</v>
+        <v>425.05234806760319</v>
       </c>
       <c r="H27">
-        <v>794.3378486799686</v>
+        <v>436.23696173868791</v>
       </c>
       <c r="I27">
-        <v>770.55690235356531</v>
+        <v>425.47994070515438</v>
       </c>
       <c r="J27">
-        <v>767.9589927130861</v>
+        <v>427.64543151225331</v>
       </c>
       <c r="K27">
-        <v>797.49930239716628</v>
+        <v>430.57808143123412</v>
       </c>
       <c r="L27">
-        <v>826.76671951153935</v>
+        <v>437.66111954049887</v>
       </c>
       <c r="M27">
-        <v>849.48678802402208</v>
+        <v>435.22134759477541</v>
       </c>
       <c r="N27">
-        <v>875.68353098615762</v>
+        <v>437.41027613776282</v>
       </c>
       <c r="O27">
-        <v>852.27743207989238</v>
+        <v>439.5661924980235</v>
       </c>
       <c r="P27">
-        <v>885.8326949892587</v>
+        <v>452.4984131649224</v>
       </c>
       <c r="Q27">
-        <v>900.18828646372879</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+        <v>462.26582850781068</v>
+      </c>
+      <c r="R27">
+        <v>457.97517376498598</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B28">
-        <v>456.76702342732068</v>
+        <v>430.29423220159799</v>
       </c>
       <c r="C28">
-        <v>494.17183248794657</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D28">
-        <v>457.27266084780928</v>
+        <v>494.64222480497858</v>
       </c>
       <c r="E28">
-        <v>436.54842669272699</v>
+        <v>455.1912450537651</v>
       </c>
       <c r="F28">
-        <v>422.05255764783612</v>
+        <v>427.74610451523068</v>
       </c>
       <c r="G28">
-        <v>435.54647590084801</v>
+        <v>406.71737376758568</v>
       </c>
       <c r="H28">
-        <v>438.41935248780209</v>
+        <v>411.69255751393308</v>
       </c>
       <c r="I28">
-        <v>439.07349964681401</v>
+        <v>405.38427269876149</v>
       </c>
       <c r="J28">
-        <v>450.30890280850309</v>
+        <v>409.52099869363889</v>
       </c>
       <c r="K28">
-        <v>436.91940145684191</v>
+        <v>425.43451413305291</v>
       </c>
       <c r="L28">
-        <v>431.0416989452325</v>
+        <v>404.10694012548612</v>
       </c>
       <c r="M28">
-        <v>440.03087847272047</v>
+        <v>398.38210615079493</v>
       </c>
       <c r="N28">
-        <v>457.44811672984127</v>
+        <v>392.01581482771809</v>
       </c>
       <c r="O28">
-        <v>474.91856432206771</v>
+        <v>400.42623871273122</v>
       </c>
       <c r="P28">
-        <v>486.67515518597941</v>
+        <v>406.86830888069522</v>
       </c>
       <c r="Q28">
-        <v>507.33804161939292</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+        <v>416.72598300455923</v>
+      </c>
+      <c r="R28">
+        <v>442.78052292664711</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B29">
-        <v>420.7687677324667</v>
+        <v>429.73881575881171</v>
       </c>
       <c r="C29">
-        <v>493.77165946943092</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D29">
-        <v>454.62227371530167</v>
+        <v>496.00660054508808</v>
       </c>
       <c r="E29">
-        <v>427.32120370872269</v>
+        <v>458.01715071133287</v>
       </c>
       <c r="F29">
-        <v>405.35568849387249</v>
+        <v>431.05029201747891</v>
       </c>
       <c r="G29">
-        <v>410.8258621617735</v>
+        <v>409.00513730441969</v>
       </c>
       <c r="H29">
-        <v>401.93001585206599</v>
+        <v>412.96228622713141</v>
       </c>
       <c r="I29">
-        <v>405.64145353623059</v>
+        <v>405.84198940375518</v>
       </c>
       <c r="J29">
-        <v>415.37865421183159</v>
+        <v>409.31113030625181</v>
       </c>
       <c r="K29">
-        <v>390.62503402724928</v>
+        <v>425.43339098364532</v>
       </c>
       <c r="L29">
-        <v>387.97458996340691</v>
+        <v>404.53074478020909</v>
       </c>
       <c r="M29">
-        <v>387.31089439503069</v>
+        <v>398.25535691114828</v>
       </c>
       <c r="N29">
-        <v>400.75658368267023</v>
+        <v>391.8871225725099</v>
       </c>
       <c r="O29">
-        <v>410.75976651561689</v>
+        <v>401.28954167174498</v>
       </c>
       <c r="P29">
-        <v>426.73266102578373</v>
+        <v>409.25882832166792</v>
       </c>
       <c r="Q29">
-        <v>445.07851221532837</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+        <v>418.04708589139199</v>
+      </c>
+      <c r="R29">
+        <v>447.05018270223599</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B30">
-        <v>465.6684750894326</v>
+        <v>427.13842390287948</v>
       </c>
       <c r="C30">
-        <v>485.12868282872671</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D30">
-        <v>465.87779754366028</v>
+        <v>495.31856915464658</v>
       </c>
       <c r="E30">
-        <v>444.11467723171</v>
+        <v>456.68066540018049</v>
       </c>
       <c r="F30">
-        <v>424.79342373132027</v>
+        <v>429.09142796730299</v>
       </c>
       <c r="G30">
-        <v>436.60770760423981</v>
+        <v>408.08531342717009</v>
       </c>
       <c r="H30">
-        <v>425.77261427997172</v>
+        <v>411.50713811234732</v>
       </c>
       <c r="I30">
-        <v>428.07372646491388</v>
+        <v>407.13184847351869</v>
       </c>
       <c r="J30">
-        <v>428.55499844264278</v>
+        <v>408.75562715066218</v>
       </c>
       <c r="K30">
-        <v>429.60770961326273</v>
+        <v>424.47838760567709</v>
       </c>
       <c r="L30">
-        <v>421.27494911215672</v>
+        <v>404.06406450290359</v>
       </c>
       <c r="M30">
-        <v>425.46430621359082</v>
+        <v>399.53944421792488</v>
       </c>
       <c r="N30">
-        <v>429.79714235172167</v>
+        <v>391.3724929438896</v>
       </c>
       <c r="O30">
-        <v>444.14147644336367</v>
+        <v>399.37142438148709</v>
       </c>
       <c r="P30">
-        <v>460.85370888422329</v>
+        <v>406.51339770759972</v>
       </c>
       <c r="Q30">
-        <v>479.43358451421062</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+        <v>417.39490915836541</v>
+      </c>
+      <c r="R30">
+        <v>444.43070459446221</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B31">
-        <v>475.92207834471589</v>
+        <v>426.53558568696928</v>
       </c>
       <c r="C31">
-        <v>483.47429882503769</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D31">
-        <v>464.29259348930839</v>
+        <v>495.87371770117539</v>
       </c>
       <c r="E31">
-        <v>442.23233115470151</v>
+        <v>456.78130205503112</v>
       </c>
       <c r="F31">
-        <v>423.37056581771918</v>
+        <v>429.42236593260412</v>
       </c>
       <c r="G31">
-        <v>434.67799962827218</v>
+        <v>407.79412393703149</v>
       </c>
       <c r="H31">
-        <v>424.84200347677108</v>
+        <v>414.22649376172711</v>
       </c>
       <c r="I31">
-        <v>427.16341391291229</v>
+        <v>408.50790676081277</v>
       </c>
       <c r="J31">
-        <v>430.40270426054792</v>
+        <v>411.13688647301552</v>
       </c>
       <c r="K31">
-        <v>435.96861976120658</v>
+        <v>430.28116643282539</v>
       </c>
       <c r="L31">
-        <v>432.8586854416526</v>
+        <v>407.34300834942883</v>
       </c>
       <c r="M31">
-        <v>434.62377349596721</v>
+        <v>399.68411241139972</v>
       </c>
       <c r="N31">
-        <v>436.14903126769121</v>
+        <v>390.95390822418699</v>
       </c>
       <c r="O31">
-        <v>447.76384453351392</v>
+        <v>400.21448899070128</v>
       </c>
       <c r="P31">
-        <v>459.56851677981513</v>
+        <v>407.37836240090138</v>
       </c>
       <c r="Q31">
-        <v>454.89423344515592</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+        <v>413.43161452788502</v>
+      </c>
+      <c r="R31">
+        <v>438.99246460971511</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B32">
-        <v>427.09381209626702</v>
+        <v>429.62904861225928</v>
       </c>
       <c r="C32">
-        <v>494.37305272395048</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D32">
-        <v>455.08624171496763</v>
+        <v>494.7345281421089</v>
       </c>
       <c r="E32">
-        <v>428.59012527078221</v>
+        <v>456.08890802343052</v>
       </c>
       <c r="F32">
-        <v>407.40337249661337</v>
+        <v>428.8022675975439</v>
       </c>
       <c r="G32">
-        <v>412.16106055223833</v>
+        <v>406.85665211860902</v>
       </c>
       <c r="H32">
-        <v>405.98891780366188</v>
+        <v>412.66711435187511</v>
       </c>
       <c r="I32">
-        <v>407.72299902940819</v>
+        <v>404.9468442929321</v>
       </c>
       <c r="J32">
-        <v>423.47310345210713</v>
+        <v>409.782725186454</v>
       </c>
       <c r="K32">
-        <v>404.90842001861802</v>
+        <v>424.94520294550159</v>
       </c>
       <c r="L32">
-        <v>396.84348856835061</v>
+        <v>403.91743557636642</v>
       </c>
       <c r="M32">
-        <v>390.013436851584</v>
+        <v>400.06484817848099</v>
       </c>
       <c r="N32">
-        <v>397.69239661201698</v>
+        <v>397.29713303499028</v>
       </c>
       <c r="O32">
-        <v>404.180863404148</v>
+        <v>406.26212710884249</v>
       </c>
       <c r="P32">
-        <v>412.85644634289991</v>
+        <v>411.38576517436331</v>
       </c>
       <c r="Q32">
-        <v>437.70832851392129</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+        <v>420.76151351636531</v>
+      </c>
+      <c r="R32">
+        <v>441.43802792480028</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B33">
-        <v>428.87737112203843</v>
+        <v>431.21385684732581</v>
       </c>
       <c r="C33">
-        <v>495.67849965333733</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D33">
-        <v>456.87556581808508</v>
+        <v>494.53395271059298</v>
       </c>
       <c r="E33">
-        <v>428.86968988620117</v>
+        <v>456.00867009087659</v>
       </c>
       <c r="F33">
-        <v>407.58180340756121</v>
+        <v>429.27476287251551</v>
       </c>
       <c r="G33">
-        <v>410.63300342282918</v>
+        <v>406.91252376102841</v>
       </c>
       <c r="H33">
-        <v>404.41245783135651</v>
+        <v>412.60778652668102</v>
       </c>
       <c r="I33">
-        <v>406.22278232594141</v>
+        <v>405.07231763933089</v>
       </c>
       <c r="J33">
-        <v>421.87743489112569</v>
+        <v>409.4035203291279</v>
       </c>
       <c r="K33">
-        <v>402.50920768870452</v>
+        <v>423.0635546317942</v>
       </c>
       <c r="L33">
-        <v>395.55352071837598</v>
+        <v>403.62944599880848</v>
       </c>
       <c r="M33">
-        <v>390.7406805766098</v>
+        <v>398.80943206371347</v>
       </c>
       <c r="N33">
-        <v>399.31455837744687</v>
+        <v>395.49669021374422</v>
       </c>
       <c r="O33">
-        <v>405.34443819085641</v>
+        <v>403.19406139305107</v>
       </c>
       <c r="P33">
-        <v>417.30565899550828</v>
+        <v>410.1488404458546</v>
       </c>
       <c r="Q33">
-        <v>445.85725167522929</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+        <v>419.15758407644518</v>
+      </c>
+      <c r="R33">
+        <v>442.18601477505359</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B34">
-        <v>432.043565396247</v>
+        <v>431.50518713131407</v>
       </c>
       <c r="C34">
-        <v>494.67923412445691</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D34">
-        <v>455.5573190231155</v>
+        <v>494.42279459224977</v>
       </c>
       <c r="E34">
-        <v>428.30361828675279</v>
+        <v>455.27479000360393</v>
       </c>
       <c r="F34">
-        <v>406.74468389740099</v>
+        <v>428.0909936953276</v>
       </c>
       <c r="G34">
-        <v>411.43538835200007</v>
+        <v>406.61287248722772</v>
       </c>
       <c r="H34">
-        <v>405.54574771790891</v>
+        <v>411.81416954134681</v>
       </c>
       <c r="I34">
-        <v>407.28637652555472</v>
+        <v>403.55144075149371</v>
       </c>
       <c r="J34">
-        <v>426.77322426435808</v>
+        <v>407.47463140133431</v>
       </c>
       <c r="K34">
-        <v>405.42615164355499</v>
+        <v>420.76069082845731</v>
       </c>
       <c r="L34">
-        <v>397.89998254173611</v>
+        <v>402.98368183174222</v>
       </c>
       <c r="M34">
-        <v>390.63373121453492</v>
+        <v>397.33573772331351</v>
       </c>
       <c r="N34">
-        <v>399.43590544563318</v>
+        <v>394.05311046312067</v>
       </c>
       <c r="O34">
-        <v>405.43612655944679</v>
+        <v>402.06319070841391</v>
       </c>
       <c r="P34">
-        <v>414.02711247412759</v>
+        <v>409.11349327331379</v>
       </c>
       <c r="Q34">
-        <v>440.72378196602261</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+        <v>418.59675243246102</v>
+      </c>
+      <c r="R34">
+        <v>441.58463095672681</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B35">
-        <v>426.25168651465327</v>
+        <v>427.74570692256589</v>
       </c>
       <c r="C35">
-        <v>495.65062423528752</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D35">
-        <v>456.41151842368828</v>
+        <v>495.87491844537601</v>
       </c>
       <c r="E35">
-        <v>429.10801336826188</v>
+        <v>456.93054174696022</v>
       </c>
       <c r="F35">
-        <v>406.63696130211531</v>
+        <v>428.84303406783579</v>
       </c>
       <c r="G35">
-        <v>410.4172225671611</v>
+        <v>407.17561125076679</v>
       </c>
       <c r="H35">
-        <v>405.00820279790571</v>
+        <v>412.46759155553912</v>
       </c>
       <c r="I35">
-        <v>407.33362023855631</v>
+        <v>406.99927725872101</v>
       </c>
       <c r="J35">
-        <v>425.84966111379111</v>
+        <v>409.38126532779842</v>
       </c>
       <c r="K35">
-        <v>406.41888736486811</v>
+        <v>423.64143850661338</v>
       </c>
       <c r="L35">
-        <v>398.11535753396981</v>
+        <v>403.39066997285039</v>
       </c>
       <c r="M35">
-        <v>387.77742605056699</v>
+        <v>399.47358213823787</v>
       </c>
       <c r="N35">
-        <v>397.3212467026388</v>
+        <v>393.51263082152582</v>
       </c>
       <c r="O35">
-        <v>402.91321841710692</v>
+        <v>402.44823835961762</v>
       </c>
       <c r="P35">
-        <v>409.6044598621292</v>
+        <v>406.81001124110492</v>
       </c>
       <c r="Q35">
-        <v>432.57458423306662</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+        <v>416.93477176444668</v>
+      </c>
+      <c r="R35">
+        <v>439.97833897432599</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B36">
-        <v>428.52075688588093</v>
+        <v>430.04417358528917</v>
       </c>
       <c r="C36">
-        <v>494.63227210524548</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D36">
-        <v>455.50515580134248</v>
+        <v>495.35157218109907</v>
       </c>
       <c r="E36">
-        <v>427.32285231030738</v>
+        <v>456.10444243516702</v>
       </c>
       <c r="F36">
-        <v>406.06542118335523</v>
+        <v>429.48531284630099</v>
       </c>
       <c r="G36">
-        <v>411.17890784664542</v>
+        <v>408.08059835665358</v>
       </c>
       <c r="H36">
-        <v>403.77649669194687</v>
+        <v>413.66429136584378</v>
       </c>
       <c r="I36">
-        <v>407.88208192982933</v>
+        <v>407.2030932790891</v>
       </c>
       <c r="J36">
-        <v>423.64960752975719</v>
+        <v>410.73583076428008</v>
       </c>
       <c r="K36">
-        <v>403.49267460428359</v>
+        <v>430.84992795677363</v>
       </c>
       <c r="L36">
-        <v>397.3160384577622</v>
+        <v>409.73210821806691</v>
       </c>
       <c r="M36">
-        <v>395.66325442071877</v>
+        <v>402.11243572976252</v>
       </c>
       <c r="N36">
-        <v>404.87437301583333</v>
+        <v>391.97053237498471</v>
       </c>
       <c r="O36">
-        <v>411.41750955890262</v>
+        <v>400.64286272314217</v>
       </c>
       <c r="P36">
-        <v>420.49600138236491</v>
+        <v>406.15075197021798</v>
       </c>
       <c r="Q36">
-        <v>440.20216979661137</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+        <v>413.03502216388227</v>
+      </c>
+      <c r="R36">
+        <v>442.55926471286688</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B37">
-        <v>432.72085703487443</v>
+        <v>448.18023630100038</v>
       </c>
       <c r="C37">
-        <v>496.45858892609908</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D37">
-        <v>457.0392675820936</v>
+        <v>482.90821057043678</v>
       </c>
       <c r="E37">
-        <v>429.54593136850679</v>
+        <v>447.70168274001122</v>
       </c>
       <c r="F37">
-        <v>407.89064212827702</v>
+        <v>414.65497281024631</v>
       </c>
       <c r="G37">
-        <v>413.08406962792208</v>
+        <v>417.07795002417089</v>
       </c>
       <c r="H37">
-        <v>407.42407991125009</v>
+        <v>438.60246262376432</v>
       </c>
       <c r="I37">
-        <v>410.44175211475249</v>
+        <v>470.90474512792662</v>
       </c>
       <c r="J37">
-        <v>423.80607348280142</v>
+        <v>465.78947332709453</v>
       </c>
       <c r="K37">
-        <v>404.4407173088054</v>
+        <v>470.79787998158753</v>
       </c>
       <c r="L37">
-        <v>401.32838085824358</v>
+        <v>483.21041193557028</v>
       </c>
       <c r="M37">
-        <v>396.18011638317068</v>
+        <v>484.16540901099171</v>
       </c>
       <c r="N37">
-        <v>404.54442877138041</v>
+        <v>490.95960470755631</v>
       </c>
       <c r="O37">
-        <v>410.04732536971028</v>
+        <v>489.86143856719059</v>
       </c>
       <c r="P37">
-        <v>418.48642960504287</v>
+        <v>499.68992777834291</v>
       </c>
       <c r="Q37">
-        <v>440.74964431849628</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+        <v>508.54368191582222</v>
+      </c>
+      <c r="R37">
+        <v>513.04761602530198</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B38">
-        <v>428.06407669529312</v>
+        <v>441.938046744497</v>
       </c>
       <c r="C38">
-        <v>494.74012795388859</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D38">
-        <v>455.71271140785723</v>
+        <v>482.08036810097138</v>
       </c>
       <c r="E38">
-        <v>427.90107804880512</v>
+        <v>441.7726933777476</v>
       </c>
       <c r="F38">
-        <v>406.2643978043929</v>
+        <v>411.85272030224161</v>
       </c>
       <c r="G38">
-        <v>410.45229976674551</v>
+        <v>413.54160950031849</v>
       </c>
       <c r="H38">
-        <v>403.24868166967678</v>
+        <v>437.85814664611149</v>
       </c>
       <c r="I38">
-        <v>407.83315204095499</v>
+        <v>463.18589572586552</v>
       </c>
       <c r="J38">
-        <v>420.24387224718072</v>
+        <v>446.65458984081857</v>
       </c>
       <c r="K38">
-        <v>402.02412978322923</v>
+        <v>452.53014297864547</v>
       </c>
       <c r="L38">
-        <v>396.61925516357672</v>
+        <v>446.83743978597897</v>
       </c>
       <c r="M38">
-        <v>392.48871037686342</v>
+        <v>432.48132802886943</v>
       </c>
       <c r="N38">
-        <v>399.21761853004261</v>
+        <v>434.62178650094529</v>
       </c>
       <c r="O38">
-        <v>406.24212420422037</v>
+        <v>438.62546700584443</v>
       </c>
       <c r="P38">
-        <v>415.33976573658111</v>
+        <v>439.06545977227222</v>
       </c>
       <c r="Q38">
-        <v>438.87990756194063</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+        <v>449.34111417495518</v>
+      </c>
+      <c r="R38">
+        <v>470.48993616783378</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B39">
-        <v>427.84451272018521</v>
+        <v>445.52735951013773</v>
       </c>
       <c r="C39">
-        <v>495.47381552076371</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D39">
-        <v>456.7496963900864</v>
+        <v>483.3591480251871</v>
       </c>
       <c r="E39">
-        <v>429.87640739410182</v>
+        <v>446.71026529437432</v>
       </c>
       <c r="F39">
-        <v>407.3478062416811</v>
+        <v>414.29351562754522</v>
       </c>
       <c r="G39">
-        <v>412.32267653932308</v>
+        <v>416.92740258910419</v>
       </c>
       <c r="H39">
-        <v>406.69930839040052</v>
+        <v>440.18836235095881</v>
       </c>
       <c r="I39">
-        <v>408.81641850418782</v>
+        <v>467.28825453362151</v>
       </c>
       <c r="J39">
-        <v>424.86725846151808</v>
+        <v>446.25218679640608</v>
       </c>
       <c r="K39">
-        <v>405.38514499827119</v>
+        <v>450.65384455226013</v>
       </c>
       <c r="L39">
-        <v>398.82994764451041</v>
+        <v>453.54944038238301</v>
       </c>
       <c r="M39">
-        <v>393.90453885403377</v>
+        <v>449.38084858125387</v>
       </c>
       <c r="N39">
-        <v>401.8789883840949</v>
+        <v>448.99444896046549</v>
       </c>
       <c r="O39">
-        <v>407.81476260757341</v>
+        <v>452.56915126494272</v>
       </c>
       <c r="P39">
-        <v>413.83970525579952</v>
+        <v>450.47608916176432</v>
       </c>
       <c r="Q39">
-        <v>436.84715030377248</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+        <v>453.12571036794787</v>
+      </c>
+      <c r="R39">
+        <v>470.77339736955008</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B40">
-        <v>425.68945033940759</v>
+        <v>502.27950725927758</v>
       </c>
       <c r="C40">
-        <v>495.50640188137322</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D40">
-        <v>455.66220814531601</v>
+        <v>504.61551210807397</v>
       </c>
       <c r="E40">
-        <v>427.48810560199871</v>
+        <v>507.04083634664369</v>
       </c>
       <c r="F40">
-        <v>405.86096694871611</v>
+        <v>486.96830318543903</v>
       </c>
       <c r="G40">
-        <v>409.14514020912878</v>
+        <v>450.80867898645357</v>
       </c>
       <c r="H40">
-        <v>403.61616407148767</v>
+        <v>448.02090040582851</v>
       </c>
       <c r="I40">
-        <v>406.79292435144129</v>
+        <v>446.54379711460228</v>
       </c>
       <c r="J40">
-        <v>423.8772110354584</v>
+        <v>461.01419261806262</v>
       </c>
       <c r="K40">
-        <v>403.60748961532579</v>
+        <v>463.59022484878079</v>
       </c>
       <c r="L40">
-        <v>397.51917770222911</v>
+        <v>471.72807600423118</v>
       </c>
       <c r="M40">
-        <v>388.23998911597238</v>
+        <v>489.24112940168209</v>
       </c>
       <c r="N40">
-        <v>397.5604471078608</v>
+        <v>510.41333750007732</v>
       </c>
       <c r="O40">
-        <v>403.94727252422422</v>
+        <v>531.54409658428881</v>
       </c>
       <c r="P40">
-        <v>411.53579652257821</v>
+        <v>549.19848386153205</v>
       </c>
       <c r="Q40">
-        <v>440.73852498973167</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+        <v>567.49227620579893</v>
+      </c>
+      <c r="R40">
+        <v>592.00241100656172</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B41">
-        <v>450.68369752030878</v>
+        <v>513.5310680051623</v>
       </c>
       <c r="C41">
-        <v>482.9409627904414</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D41">
-        <v>447.38778987618679</v>
+        <v>512.49850882715498</v>
       </c>
       <c r="E41">
-        <v>415.53581579466402</v>
+        <v>489.46910545042522</v>
       </c>
       <c r="F41">
-        <v>418.7920986241628</v>
+        <v>500.14490591551521</v>
       </c>
       <c r="G41">
-        <v>441.57648364390963</v>
+        <v>518.24931220242195</v>
       </c>
       <c r="H41">
-        <v>475.48122876982723</v>
+        <v>544.83547610610515</v>
       </c>
       <c r="I41">
-        <v>470.51339021955221</v>
+        <v>555.01040423091513</v>
       </c>
       <c r="J41">
-        <v>477.92195557775142</v>
+        <v>549.71282128954647</v>
       </c>
       <c r="K41">
-        <v>488.1070671994537</v>
+        <v>543.63613211642382</v>
       </c>
       <c r="L41">
-        <v>489.52316780137909</v>
+        <v>547.60739667653957</v>
       </c>
       <c r="M41">
-        <v>500.85403575251672</v>
+        <v>578.32671676137579</v>
       </c>
       <c r="N41">
-        <v>499.90443675140358</v>
+        <v>607.42041957585514</v>
       </c>
       <c r="O41">
-        <v>508.5716189256774</v>
+        <v>620.58715190460896</v>
       </c>
       <c r="P41">
-        <v>518.57721618467872</v>
+        <v>638.43293052271849</v>
       </c>
       <c r="Q41">
-        <v>524.27000990802935</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+        <v>650.59382115230767</v>
+      </c>
+      <c r="R41">
+        <v>644.54214332751212</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B42">
-        <v>435.80833551987018</v>
+        <v>511.246972853898</v>
       </c>
       <c r="C42">
-        <v>482.21321245075922</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D42">
-        <v>439.77906214025558</v>
+        <v>565.75192976995061</v>
       </c>
       <c r="E42">
-        <v>408.42582454383478</v>
+        <v>502.00389075872789</v>
       </c>
       <c r="F42">
-        <v>410.6695851814714</v>
+        <v>506.89530832147977</v>
       </c>
       <c r="G42">
-        <v>435.23017780294322</v>
+        <v>506.29777432745323</v>
       </c>
       <c r="H42">
-        <v>462.02085428059411</v>
+        <v>530.23587872319558</v>
       </c>
       <c r="I42">
-        <v>446.2981560628578</v>
+        <v>522.67915120462703</v>
       </c>
       <c r="J42">
-        <v>449.43723256734881</v>
+        <v>521.85472907667872</v>
       </c>
       <c r="K42">
-        <v>448.11789635888562</v>
+        <v>548.98394847320105</v>
       </c>
       <c r="L42">
-        <v>434.73759619651992</v>
+        <v>581.33415902117304</v>
       </c>
       <c r="M42">
-        <v>435.36580016024141</v>
+        <v>614.22030099174992</v>
       </c>
       <c r="N42">
-        <v>440.66993581296481</v>
+        <v>622.43266094892601</v>
       </c>
       <c r="O42">
-        <v>442.96988692791638</v>
+        <v>624.35440781905572</v>
       </c>
       <c r="P42">
-        <v>454.02793601858929</v>
+        <v>635.71340318580712</v>
       </c>
       <c r="Q42">
-        <v>474.28995970929748</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+        <v>640.04053616193494</v>
+      </c>
+      <c r="R42">
+        <v>637.70778686853544</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B43">
-        <v>442.32659702250572</v>
+        <v>504.63326268794941</v>
       </c>
       <c r="C43">
-        <v>481.0167312783513</v>
+        <v>762.5086417681257</v>
       </c>
       <c r="D43">
-        <v>441.24826307510261</v>
+        <v>499.07387117175881</v>
       </c>
       <c r="E43">
-        <v>408.82450439230189</v>
+        <v>504.25142641167622</v>
       </c>
       <c r="F43">
-        <v>412.22182268789783</v>
+        <v>510.91134926579127</v>
       </c>
       <c r="G43">
-        <v>433.6785518582393</v>
+        <v>521.42982640908463</v>
       </c>
       <c r="H43">
-        <v>460.40702280673901</v>
+        <v>561.51322760893402</v>
       </c>
       <c r="I43">
-        <v>441.07109911681999</v>
+        <v>549.60757341845999</v>
       </c>
       <c r="J43">
-        <v>443.49895614629162</v>
+        <v>539.00621078840413</v>
       </c>
       <c r="K43">
-        <v>446.41214603835527</v>
+        <v>526.58359015846645</v>
       </c>
       <c r="L43">
-        <v>441.6193332940976</v>
+        <v>556.71988691557624</v>
       </c>
       <c r="M43">
-        <v>440.70506252652581</v>
+        <v>555.69875412474448</v>
       </c>
       <c r="N43">
-        <v>444.07180821685063</v>
+        <v>576.22232823061529</v>
       </c>
       <c r="O43">
-        <v>442.81916592131898</v>
+        <v>579.26496316052715</v>
       </c>
       <c r="P43">
-        <v>446.93003454809082</v>
+        <v>575.21540590201255</v>
       </c>
       <c r="Q43">
-        <v>461.46397438213438</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>59</v>
-      </c>
-      <c r="B44">
-        <v>507.25807032494629</v>
-      </c>
-      <c r="C44">
-        <v>505.79624157869279</v>
-      </c>
-      <c r="D44">
-        <v>508.60157032971239</v>
-      </c>
-      <c r="E44">
-        <v>486.91024516055961</v>
-      </c>
-      <c r="F44">
-        <v>451.52296768129798</v>
-      </c>
-      <c r="G44">
-        <v>451.05314401237109</v>
-      </c>
-      <c r="H44">
-        <v>450.36548207230442</v>
-      </c>
-      <c r="I44">
-        <v>464.99263375489397</v>
-      </c>
-      <c r="J44">
-        <v>467.63652983968689</v>
-      </c>
-      <c r="K44">
-        <v>473.90961413018431</v>
-      </c>
-      <c r="L44">
-        <v>491.34990379593847</v>
-      </c>
-      <c r="M44">
-        <v>514.40144046184776</v>
-      </c>
-      <c r="N44">
-        <v>534.71344667617154</v>
-      </c>
-      <c r="O44">
-        <v>552.05066909695097</v>
-      </c>
-      <c r="P44">
-        <v>569.40761797673554</v>
-      </c>
-      <c r="Q44">
-        <v>592.3280591390436</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B45">
-        <v>513.38390433023756</v>
-      </c>
-      <c r="C45">
-        <v>513.10745019198544</v>
-      </c>
-      <c r="D45">
-        <v>490.03437976568188</v>
-      </c>
-      <c r="E45">
-        <v>501.01839291393009</v>
-      </c>
-      <c r="F45">
-        <v>518.23143610953775</v>
-      </c>
-      <c r="G45">
-        <v>544.40693872943291</v>
-      </c>
-      <c r="H45">
-        <v>556.88396919924469</v>
-      </c>
-      <c r="I45">
-        <v>551.7238199889382</v>
-      </c>
-      <c r="J45">
-        <v>545.90893977653502</v>
-      </c>
-      <c r="K45">
-        <v>550.91560124283251</v>
-      </c>
-      <c r="L45">
-        <v>583.49622745257159</v>
-      </c>
-      <c r="M45">
-        <v>610.47704092177344</v>
-      </c>
-      <c r="N45">
-        <v>623.05743141562277</v>
-      </c>
-      <c r="O45">
-        <v>640.00555802827057</v>
-      </c>
-      <c r="P45">
-        <v>648.74079818774499</v>
-      </c>
-      <c r="Q45">
-        <v>639.71203734930657</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B46">
-        <v>507.00308892589658</v>
-      </c>
-      <c r="C46">
-        <v>565.56317396232589</v>
-      </c>
-      <c r="D46">
-        <v>501.58453743992612</v>
-      </c>
-      <c r="E46">
-        <v>507.92178773301509</v>
-      </c>
-      <c r="F46">
-        <v>506.17028349214081</v>
-      </c>
-      <c r="G46">
-        <v>532.20739884617694</v>
-      </c>
-      <c r="H46">
-        <v>524.90159115525057</v>
-      </c>
-      <c r="I46">
-        <v>523.3621367991459</v>
-      </c>
-      <c r="J46">
-        <v>551.41664760531944</v>
-      </c>
-      <c r="K46">
-        <v>585.31605194693407</v>
-      </c>
-      <c r="L46">
-        <v>619.46280924756854</v>
-      </c>
-      <c r="M46">
-        <v>626.86511368334266</v>
-      </c>
-      <c r="N46">
-        <v>628.64133724928956</v>
-      </c>
-      <c r="O46">
-        <v>639.70344227604039</v>
-      </c>
-      <c r="P46">
-        <v>645.3309333520798</v>
-      </c>
-      <c r="Q46">
-        <v>645.05065323527651</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47">
-        <v>504.35793222476332</v>
-      </c>
-      <c r="C47">
-        <v>498.51863189358681</v>
-      </c>
-      <c r="D47">
-        <v>503.81786258754028</v>
-      </c>
-      <c r="E47">
-        <v>508.63163409690242</v>
-      </c>
-      <c r="F47">
-        <v>518.30512207574384</v>
-      </c>
-      <c r="G47">
-        <v>557.4031818631596</v>
-      </c>
-      <c r="H47">
-        <v>546.99843610344294</v>
-      </c>
-      <c r="I47">
-        <v>536.04887025428172</v>
-      </c>
-      <c r="J47">
-        <v>522.03989109006579</v>
-      </c>
-      <c r="K47">
-        <v>549.83743009896136</v>
-      </c>
-      <c r="L47">
-        <v>548.21776728434384</v>
-      </c>
-      <c r="M47">
-        <v>566.90555001110215</v>
-      </c>
-      <c r="N47">
-        <v>571.90389517595543</v>
-      </c>
-      <c r="O47">
-        <v>568.9155471660298</v>
-      </c>
-      <c r="P47">
-        <v>569.73739138421229</v>
-      </c>
-      <c r="Q47">
-        <v>568.14272590996393</v>
+        <v>575.29728259501564</v>
+      </c>
+      <c r="R43">
+        <v>573.64132577732903</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:Q47">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="C2:R43">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3089,7 +2979,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="top10" dxfId="0" priority="1" bottom="1" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
